--- a/public/tests/data/test_rb_sigma.xlsx
+++ b/public/tests/data/test_rb_sigma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A612213-4A60-40CC-8F96-04A413AE04A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECB37A3-B6A9-4174-ADAE-FE4806820B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
   <si>
     <t>Name</t>
   </si>
@@ -89,9 +89,6 @@
     <t>P1</t>
   </si>
   <si>
-    <t>P2</t>
-  </si>
-  <si>
     <t>Asset</t>
   </si>
   <si>
@@ -164,16 +161,13 @@
     <t>_grow</t>
   </si>
   <si>
-    <t>monthly</t>
-  </si>
-  <si>
     <t>_WD</t>
   </si>
   <si>
     <t>_P1</t>
   </si>
   <si>
-    <t>_P2</t>
+    <t>sigma</t>
   </si>
 </sst>
 </file>
@@ -182,8 +176,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.0000%"/>
-    <numFmt numFmtId="173" formatCode="[$]dddd" x16r2:formatCode16="[$-en-SE]dddd"/>
+    <numFmt numFmtId="165" formatCode="0.0000%"/>
+    <numFmt numFmtId="166" formatCode="[$]dddd" x16r2:formatCode16="[$-en-SE]dddd"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -222,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -231,17 +225,15 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,7 +555,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -571,7 +563,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -639,10 +631,10 @@
         <v>9</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>37</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
@@ -1258,64 +1250,49 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955DA01E-A3C8-43F7-BE2B-2D20BB66CB4A}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3">
         <v>0.5</v>
       </c>
-      <c r="C4" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="C5" s="3">
         <v>0.5</v>
       </c>
     </row>
@@ -1326,136 +1303,98 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EA1201-9593-4FA8-BE4A-D6543E3F5A5B}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.4609375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.15234375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="E1" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="E2" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45658</v>
       </c>
-      <c r="B3" s="12">
-        <f>A3</f>
+      <c r="B3" s="11">
+        <f t="shared" ref="B3:B34" si="0">A3</f>
         <v>45658</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>0.5</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>0.5</v>
       </c>
       <c r="E3" s="7">
         <v>1</v>
       </c>
-      <c r="F3" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45659</v>
       </c>
-      <c r="B4" s="12">
-        <f>A4</f>
+      <c r="B4" s="11">
+        <f t="shared" si="0"/>
         <v>45659</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>0.5</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>0.5</v>
       </c>
       <c r="E4" s="7">
         <f xml:space="preserve"> $C4 * Prices!$D3 + $D4 * Prices!$E3</f>
         <v>0.95500000000000007</v>
       </c>
-      <c r="F4" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="7">
-        <f xml:space="preserve"> $F4 * Prices!$D3 + $G4 * Prices!$E3</f>
-        <v>0.95500000000000007</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45660</v>
       </c>
-      <c r="B5" s="12">
-        <f>A5</f>
+      <c r="B5" s="11">
+        <f t="shared" si="0"/>
         <v>45660</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <f>(C4 * Prices!D3) / $E4</f>
         <v>0.52879581151832455</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <f>(D4 * Prices!E3) / $E4</f>
         <v>0.47120418848167539</v>
       </c>
@@ -1463,32 +1402,20 @@
         <f xml:space="preserve"> $C5 * Prices!$D4 + $D5 * Prices!$E4</f>
         <v>1.0575916230366491</v>
       </c>
-      <c r="F5" s="10">
-        <f>(F4 * Prices!D3) / $H4</f>
-        <v>0.52879581151832455</v>
-      </c>
-      <c r="G5" s="10">
-        <f>(G4 * Prices!E3) / $H4</f>
-        <v>0.47120418848167539</v>
-      </c>
-      <c r="H5" s="7">
-        <f xml:space="preserve"> $F5 * Prices!$D4 + $G5 * Prices!$E4</f>
-        <v>1.0575916230366491</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45661</v>
       </c>
-      <c r="B6" s="12">
-        <f>A6</f>
+      <c r="B6" s="11">
+        <f t="shared" si="0"/>
         <v>45661</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <f>(C5 * Prices!D4) / $E5</f>
         <v>0.50495049504950495</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f>(D5 * Prices!E4) / E5</f>
         <v>0.4950495049504951</v>
       </c>
@@ -1496,32 +1423,20 @@
         <f xml:space="preserve"> $C6 * Prices!$D5 + $D6 * Prices!$E5</f>
         <v>0.95544554455445552</v>
       </c>
-      <c r="F6" s="10">
-        <f>(F5 * Prices!D4) / $H5</f>
-        <v>0.50495049504950495</v>
-      </c>
-      <c r="G6" s="10">
-        <f>(G5 * Prices!E4) / $H5</f>
-        <v>0.4950495049504951</v>
-      </c>
-      <c r="H6" s="7">
-        <f xml:space="preserve"> $F6 * Prices!$D5 + $G6 * Prices!$E5</f>
-        <v>0.95544554455445552</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45662</v>
       </c>
-      <c r="B7" s="12">
-        <f>A7</f>
+      <c r="B7" s="11">
+        <f t="shared" si="0"/>
         <v>45662</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <f>(C6 * Prices!D5) / $E6</f>
         <v>0.53367875647668395</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f>(D6 * Prices!E5) / E6</f>
         <v>0.46632124352331611</v>
       </c>
@@ -1529,63 +1444,39 @@
         <f xml:space="preserve"> $C7 * Prices!$D6 + $D7 * Prices!$E6</f>
         <v>1.0569948186528499</v>
       </c>
-      <c r="F7" s="10">
-        <f>(F6 * Prices!D5) / $H6</f>
-        <v>0.53367875647668395</v>
-      </c>
-      <c r="G7" s="10">
-        <f>(G6 * Prices!E5) / $H6</f>
-        <v>0.46632124352331611</v>
-      </c>
-      <c r="H7" s="7">
-        <f xml:space="preserve"> $F7 * Prices!$D6 + $G7 * Prices!$E6</f>
-        <v>1.0569948186528499</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45663</v>
       </c>
-      <c r="B8" s="13">
-        <f>A8</f>
+      <c r="B8" s="12">
+        <f t="shared" si="0"/>
         <v>45663</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>0.5</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>0.5</v>
       </c>
       <c r="E8" s="7">
         <f xml:space="preserve"> $C8 * Prices!$D7 + $D8 * Prices!$E7</f>
         <v>0.95480769230769225</v>
       </c>
-      <c r="F8" s="10">
-        <f>(F7 * Prices!D6) / $H7</f>
-        <v>0.50980392156862742</v>
-      </c>
-      <c r="G8" s="10">
-        <f>(G7 * Prices!E6) / $H7</f>
-        <v>0.49019607843137253</v>
-      </c>
-      <c r="H8" s="7">
-        <f xml:space="preserve"> $F8 * Prices!$D7 + $G8 * Prices!$E7</f>
-        <v>0.95588235294117641</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45664</v>
       </c>
-      <c r="B9" s="12">
-        <f>A9</f>
+      <c r="B9" s="11">
+        <f t="shared" si="0"/>
         <v>45664</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <f>(C8 * Prices!D7) / $E8</f>
         <v>0.52870090634441091</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <f>(D8 * Prices!E7) / E8</f>
         <v>0.47129909365558914</v>
       </c>
@@ -1593,32 +1484,20 @@
         <f xml:space="preserve"> $C9 * Prices!$D8 + $D9 * Prices!$E8</f>
         <v>1.0574018126888218</v>
       </c>
-      <c r="F9" s="10">
-        <f>(F8 * Prices!D7) / $H8</f>
-        <v>0.53846153846153844</v>
-      </c>
-      <c r="G9" s="10">
-        <f>(G8 * Prices!E7) / $H8</f>
-        <v>0.46153846153846156</v>
-      </c>
-      <c r="H9" s="7">
-        <f xml:space="preserve"> $F9 * Prices!$D8 + $G9 * Prices!$E8</f>
-        <v>1.0564102564102564</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45665</v>
       </c>
-      <c r="B10" s="12">
-        <f>A10</f>
+      <c r="B10" s="11">
+        <f t="shared" si="0"/>
         <v>45665</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <f>(C9 * Prices!D8) / $E9</f>
         <v>0.50476190476190474</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f>(D9 * Prices!E8) / E9</f>
         <v>0.4952380952380952</v>
       </c>
@@ -1626,32 +1505,20 @@
         <f xml:space="preserve"> $C10 * Prices!$D9 + $D10 * Prices!$E9</f>
         <v>0.95523809523809522</v>
       </c>
-      <c r="F10" s="10">
-        <f>(F9 * Prices!D8) / $H9</f>
-        <v>0.5145631067961165</v>
-      </c>
-      <c r="G10" s="10">
-        <f>(G9 * Prices!E8) / $H9</f>
-        <v>0.48543689320388356</v>
-      </c>
-      <c r="H10" s="7">
-        <f xml:space="preserve"> $F10 * Prices!$D9 + $G10 * Prices!$E9</f>
-        <v>0.95631067961165073</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45666</v>
       </c>
-      <c r="B11" s="12">
-        <f>A11</f>
+      <c r="B11" s="11">
+        <f t="shared" si="0"/>
         <v>45666</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <f>(C10 * Prices!D9) / $E10</f>
         <v>0.53339980059820546</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <f>(D10 * Prices!E9) / E10</f>
         <v>0.46660019940179459</v>
       </c>
@@ -1659,32 +1526,20 @@
         <f xml:space="preserve"> $C11 * Prices!$D10 + $D11 * Prices!$E10</f>
         <v>1.0568295114656032</v>
       </c>
-      <c r="F11" s="10">
-        <f>(F10 * Prices!D9) / $H10</f>
-        <v>0.54314720812182737</v>
-      </c>
-      <c r="G11" s="10">
-        <f>(G10 * Prices!E9) / $H10</f>
-        <v>0.45685279187817257</v>
-      </c>
-      <c r="H11" s="7">
-        <f xml:space="preserve"> $F11 * Prices!$D10 + $G11 * Prices!$E10</f>
-        <v>1.0558375634517765</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45667</v>
       </c>
-      <c r="B12" s="12">
-        <f>A12</f>
+      <c r="B12" s="11">
+        <f t="shared" si="0"/>
         <v>45667</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <f>(C11 * Prices!D10) / $E11</f>
         <v>0.50943396226415094</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <f>(D11 * Prices!E10) / E11</f>
         <v>0.49056603773584906</v>
       </c>
@@ -1692,32 +1547,20 @@
         <f xml:space="preserve"> $C12 * Prices!$D11 + $D12 * Prices!$E11</f>
         <v>0.95566037735849063</v>
       </c>
-      <c r="F12" s="10">
-        <f>(F11 * Prices!D10) / $H11</f>
-        <v>0.51923076923076916</v>
-      </c>
-      <c r="G12" s="10">
-        <f>(G11 * Prices!E10) / $H11</f>
-        <v>0.48076923076923084</v>
-      </c>
-      <c r="H12" s="7">
-        <f xml:space="preserve"> $F12 * Prices!$D11 + $G12 * Prices!$E11</f>
-        <v>0.95673076923076916</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45668</v>
       </c>
-      <c r="B13" s="12">
-        <f>A13</f>
+      <c r="B13" s="11">
+        <f t="shared" si="0"/>
         <v>45668</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <f>(C12 * Prices!D11) / $E12</f>
         <v>0.53800592300098715</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <f>(D12 * Prices!E11) / E12</f>
         <v>0.46199407699901279</v>
       </c>
@@ -1725,32 +1568,20 @@
         <f xml:space="preserve"> $C13 * Prices!$D12 + $D13 * Prices!$E12</f>
         <v>1.0562685093780848</v>
       </c>
-      <c r="F13" s="10">
-        <f>(F12 * Prices!D11) / $H12</f>
-        <v>0.54773869346733661</v>
-      </c>
-      <c r="G13" s="10">
-        <f>(G12 * Prices!E11) / $H12</f>
-        <v>0.45226130653266344</v>
-      </c>
-      <c r="H13" s="7">
-        <f xml:space="preserve"> $F13 * Prices!$D12 + $G13 * Prices!$E12</f>
-        <v>1.0552763819095479</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45669</v>
       </c>
-      <c r="B14" s="12">
-        <f>A14</f>
+      <c r="B14" s="11">
+        <f t="shared" si="0"/>
         <v>45669</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <f>(C13 * Prices!D12) / $E13</f>
         <v>0.51401869158878499</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <f>(D13 * Prices!E12) / E13</f>
         <v>0.48598130841121495</v>
       </c>
@@ -1758,63 +1589,39 @@
         <f xml:space="preserve"> $C14 * Prices!$D13 + $D14 * Prices!$E13</f>
         <v>0.9560747663551401</v>
       </c>
-      <c r="F14" s="10">
-        <f>(F13 * Prices!D12) / $H13</f>
-        <v>0.52380952380952372</v>
-      </c>
-      <c r="G14" s="10">
-        <f>(G13 * Prices!E12) / $H13</f>
-        <v>0.47619047619047628</v>
-      </c>
-      <c r="H14" s="7">
-        <f xml:space="preserve"> $F14 * Prices!$D13 + $G14 * Prices!$E13</f>
-        <v>0.95714285714285707</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45670</v>
       </c>
-      <c r="B15" s="13">
-        <f>A15</f>
+      <c r="B15" s="12">
+        <f t="shared" si="0"/>
         <v>45670</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <v>0.5</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>0.5</v>
       </c>
       <c r="E15" s="7">
         <f xml:space="preserve"> $C15 * Prices!$D14 + $D15 * Prices!$E14</f>
         <v>1.06006006006006</v>
       </c>
-      <c r="F15" s="10">
-        <f>(F14 * Prices!D13) / $H14</f>
-        <v>0.55223880597014918</v>
-      </c>
-      <c r="G15" s="10">
-        <f>(G14 * Prices!E13) / $H14</f>
-        <v>0.44776119402985087</v>
-      </c>
-      <c r="H15" s="7">
-        <f xml:space="preserve"> $F15 * Prices!$D14 + $G15 * Prices!$E14</f>
-        <v>1.0547263681592041</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45671</v>
       </c>
-      <c r="B16" s="12">
-        <f>A16</f>
+      <c r="B16" s="11">
+        <f t="shared" si="0"/>
         <v>45671</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <f>(C15 * Prices!D14) / $E15</f>
         <v>0.47592067988668552</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <f>(D15 * Prices!E14) / E15</f>
         <v>0.52407932011331448</v>
       </c>
@@ -1822,32 +1629,20 @@
         <f xml:space="preserve"> $C16 * Prices!$D15 + $D16 * Prices!$E15</f>
         <v>0.95184135977337103</v>
       </c>
-      <c r="F16" s="10">
-        <f>(F15 * Prices!D14) / $H15</f>
-        <v>0.52830188679245271</v>
-      </c>
-      <c r="G16" s="10">
-        <f>(G15 * Prices!E14) / $H15</f>
-        <v>0.47169811320754729</v>
-      </c>
-      <c r="H16" s="7">
-        <f xml:space="preserve"> $F16 * Prices!$D15 + $G16 * Prices!$E15</f>
-        <v>0.95754716981132071</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45672</v>
       </c>
-      <c r="B17" s="12">
-        <f>A17</f>
+      <c r="B17" s="11">
+        <f t="shared" si="0"/>
         <v>45672</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <f>(C16 * Prices!D15) / $E16</f>
         <v>0.5044642857142857</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <f>(D16 * Prices!E15) / E16</f>
         <v>0.49553571428571436</v>
       </c>
@@ -1855,32 +1650,20 @@
         <f xml:space="preserve"> $C17 * Prices!$D16 + $D17 * Prices!$E16</f>
         <v>1.0595238095238098</v>
       </c>
-      <c r="F17" s="10">
-        <f>(F16 * Prices!D15) / $H16</f>
-        <v>0.55665024630541859</v>
-      </c>
-      <c r="G17" s="10">
-        <f>(G16 * Prices!E15) / $H16</f>
-        <v>0.44334975369458146</v>
-      </c>
-      <c r="H17" s="7">
-        <f xml:space="preserve"> $F17 * Prices!$D16 + $G17 * Prices!$E16</f>
-        <v>1.0541871921182266</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45673</v>
       </c>
-      <c r="B18" s="12">
-        <f>A18</f>
+      <c r="B18" s="11">
+        <f t="shared" si="0"/>
         <v>45673</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <f>(C17 * Prices!D16) / $E17</f>
         <v>0.48033707865168523</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <f>(D17 * Prices!E16) / E17</f>
         <v>0.5196629213483146</v>
       </c>
@@ -1888,32 +1671,20 @@
         <f xml:space="preserve"> $C18 * Prices!$D17 + $D18 * Prices!$E17</f>
         <v>0.95224719101123578</v>
       </c>
-      <c r="F18" s="10">
-        <f>(F17 * Prices!D16) / $H17</f>
-        <v>0.53271028037383161</v>
-      </c>
-      <c r="G18" s="10">
-        <f>(G17 * Prices!E16) / $H17</f>
-        <v>0.46728971962616844</v>
-      </c>
-      <c r="H18" s="7">
-        <f xml:space="preserve"> $F18 * Prices!$D17 + $G18 * Prices!$E17</f>
-        <v>0.95794392523364502</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45674</v>
       </c>
-      <c r="B19" s="12">
-        <f>A19</f>
+      <c r="B19" s="11">
+        <f t="shared" si="0"/>
         <v>45674</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <f>(C18 * Prices!D17) / $E18</f>
         <v>0.50884955752212391</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <f>(D18 * Prices!E17) / E18</f>
         <v>0.4911504424778762</v>
       </c>
@@ -1921,32 +1692,20 @@
         <f xml:space="preserve"> $C19 * Prices!$D18 + $D19 * Prices!$E18</f>
         <v>1.0589970501474928</v>
       </c>
-      <c r="F19" s="10">
-        <f>(F18 * Prices!D17) / $H18</f>
-        <v>0.56097560975609739</v>
-      </c>
-      <c r="G19" s="10">
-        <f>(G18 * Prices!E17) / $H18</f>
-        <v>0.43902439024390261</v>
-      </c>
-      <c r="H19" s="7">
-        <f xml:space="preserve"> $F19 * Prices!$D18 + $G19 * Prices!$E18</f>
-        <v>1.0536585365853659</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45675</v>
       </c>
-      <c r="B20" s="12">
-        <f>A20</f>
+      <c r="B20" s="11">
+        <f t="shared" si="0"/>
         <v>45675</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <f>(C19 * Prices!D18) / $E19</f>
         <v>0.48467966573816151</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <f>(D19 * Prices!E18) / E19</f>
         <v>0.51532033426183854</v>
       </c>
@@ -1954,32 +1713,20 @@
         <f xml:space="preserve"> $C20 * Prices!$D19 + $D20 * Prices!$E19</f>
         <v>0.9526462395543176</v>
       </c>
-      <c r="F20" s="10">
-        <f>(F19 * Prices!D18) / $H19</f>
-        <v>0.53703703703703687</v>
-      </c>
-      <c r="G20" s="10">
-        <f>(G19 * Prices!E18) / $H19</f>
-        <v>0.46296296296296313</v>
-      </c>
-      <c r="H20" s="7">
-        <f xml:space="preserve"> $F20 * Prices!$D19 + $G20 * Prices!$E19</f>
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45676</v>
       </c>
-      <c r="B21" s="12">
-        <f>A21</f>
+      <c r="B21" s="11">
+        <f t="shared" si="0"/>
         <v>45676</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <f>(C20 * Prices!D19) / $E20</f>
         <v>0.51315789473684204</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <f>(D20 * Prices!E19) / E20</f>
         <v>0.48684210526315796</v>
       </c>
@@ -1987,63 +1734,39 @@
         <f xml:space="preserve"> $C21 * Prices!$D20 + $D21 * Prices!$E20</f>
         <v>1.0584795321637426</v>
       </c>
-      <c r="F21" s="10">
-        <f>(F20 * Prices!D19) / $H20</f>
-        <v>0.56521739130434767</v>
-      </c>
-      <c r="G21" s="10">
-        <f>(G20 * Prices!E19) / $H20</f>
-        <v>0.43478260869565233</v>
-      </c>
-      <c r="H21" s="7">
-        <f xml:space="preserve"> $F21 * Prices!$D20 + $G21 * Prices!$E20</f>
-        <v>1.0531400966183575</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45677</v>
       </c>
-      <c r="B22" s="13">
-        <f>A22</f>
+      <c r="B22" s="12">
+        <f t="shared" si="0"/>
         <v>45677</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <v>0.5</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>0.5</v>
       </c>
       <c r="E22" s="7">
         <f xml:space="preserve"> $C22 * Prices!$D21 + $D22 * Prices!$E21</f>
         <v>0.95423728813559316</v>
       </c>
-      <c r="F22" s="10">
-        <f>(F21 * Prices!D20) / $H21</f>
-        <v>0.54128440366972463</v>
-      </c>
-      <c r="G22" s="10">
-        <f>(G21 * Prices!E20) / $H21</f>
-        <v>0.45871559633027542</v>
-      </c>
-      <c r="H22" s="7">
-        <f xml:space="preserve"> $F22 * Prices!$D21 + $G22 * Prices!$E21</f>
-        <v>0.95871559633027525</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45678</v>
       </c>
-      <c r="B23" s="12">
-        <f>A23</f>
+      <c r="B23" s="11">
+        <f t="shared" si="0"/>
         <v>45678</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <f>(C22 * Prices!D21) / $E22</f>
         <v>0.52841918294849022</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <f>(D22 * Prices!E21) / E22</f>
         <v>0.47158081705150978</v>
       </c>
@@ -2051,32 +1774,20 @@
         <f xml:space="preserve"> $C23 * Prices!$D22 + $D23 * Prices!$E22</f>
         <v>1.0568383658969807</v>
       </c>
-      <c r="F23" s="10">
-        <f>(F22 * Prices!D21) / $H22</f>
-        <v>0.56937799043062187</v>
-      </c>
-      <c r="G23" s="10">
-        <f>(G22 * Prices!E21) / $H22</f>
-        <v>0.43062200956937818</v>
-      </c>
-      <c r="H23" s="7">
-        <f xml:space="preserve"> $F23 * Prices!$D22 + $G23 * Prices!$E22</f>
-        <v>1.0526315789473686</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45679</v>
       </c>
-      <c r="B24" s="12">
-        <f>A24</f>
+      <c r="B24" s="11">
+        <f t="shared" si="0"/>
         <v>45679</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9">
         <f>(C23 * Prices!D22) / $E23</f>
         <v>0.50420168067226878</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <f>(D23 * Prices!E22) / E23</f>
         <v>0.49579831932773105</v>
       </c>
@@ -2084,32 +1795,20 @@
         <f xml:space="preserve"> $C24 * Prices!$D23 + $D24 * Prices!$E23</f>
         <v>0.95462184873949563</v>
       </c>
-      <c r="F24" s="10">
-        <f>(F23 * Prices!D22) / $H23</f>
-        <v>0.5454545454545453</v>
-      </c>
-      <c r="G24" s="10">
-        <f>(G23 * Prices!E22) / $H23</f>
-        <v>0.4545454545454547</v>
-      </c>
-      <c r="H24" s="7">
-        <f xml:space="preserve"> $F24 * Prices!$D23 + $G24 * Prices!$E23</f>
-        <v>0.95909090909090899</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45680</v>
       </c>
-      <c r="B25" s="12">
-        <f>A25</f>
+      <c r="B25" s="11">
+        <f t="shared" si="0"/>
         <v>45680</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9">
         <f>(C24 * Prices!D23) / $E24</f>
         <v>0.53257042253521125</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <f>(D24 * Prices!E23) / E24</f>
         <v>0.4674295774647888</v>
       </c>
@@ -2117,32 +1816,20 @@
         <f xml:space="preserve"> $C25 * Prices!$D24 + $D25 * Prices!$E24</f>
         <v>1.0563380281690142</v>
       </c>
-      <c r="F25" s="10">
-        <f>(F24 * Prices!D23) / $H24</f>
-        <v>0.57345971563981035</v>
-      </c>
-      <c r="G25" s="10">
-        <f>(G24 * Prices!E23) / $H24</f>
-        <v>0.42654028436018976</v>
-      </c>
-      <c r="H25" s="7">
-        <f xml:space="preserve"> $F25 * Prices!$D24 + $G25 * Prices!$E24</f>
-        <v>1.0521327014218009</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45681</v>
       </c>
-      <c r="B26" s="12">
-        <f>A26</f>
+      <c r="B26" s="11">
+        <f t="shared" si="0"/>
         <v>45681</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="9">
         <f>(C25 * Prices!D24) / $E25</f>
         <v>0.5083333333333333</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <f>(D25 * Prices!E24) / E25</f>
         <v>0.49166666666666675</v>
       </c>
@@ -2150,32 +1837,20 @@
         <f xml:space="preserve"> $C26 * Prices!$D25 + $D26 * Prices!$E25</f>
         <v>0.95500000000000007</v>
       </c>
-      <c r="F26" s="10">
-        <f>(F25 * Prices!D24) / $H25</f>
-        <v>0.54954954954954938</v>
-      </c>
-      <c r="G26" s="10">
-        <f>(G25 * Prices!E24) / $H25</f>
-        <v>0.45045045045045068</v>
-      </c>
-      <c r="H26" s="7">
-        <f xml:space="preserve"> $F26 * Prices!$D25 + $G26 * Prices!$E25</f>
-        <v>0.95945945945945943</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45682</v>
       </c>
-      <c r="B27" s="12">
-        <f>A27</f>
+      <c r="B27" s="11">
+        <f t="shared" si="0"/>
         <v>45682</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="9">
         <f>(C26 * Prices!D25) / $E26</f>
         <v>0.53664921465968574</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <f>(D26 * Prices!E25) / E26</f>
         <v>0.46335078534031415</v>
       </c>
@@ -2183,32 +1858,20 @@
         <f xml:space="preserve"> $C27 * Prices!$D26 + $D27 * Prices!$E26</f>
         <v>1.0558464223385688</v>
       </c>
-      <c r="F27" s="10">
-        <f>(F26 * Prices!D25) / $H26</f>
-        <v>0.57746478873239415</v>
-      </c>
-      <c r="G27" s="10">
-        <f>(G26 * Prices!E25) / $H26</f>
-        <v>0.42253521126760585</v>
-      </c>
-      <c r="H27" s="7">
-        <f xml:space="preserve"> $F27 * Prices!$D26 + $G27 * Prices!$E26</f>
-        <v>1.051643192488263</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45683</v>
       </c>
-      <c r="B28" s="12">
-        <f>A28</f>
+      <c r="B28" s="11">
+        <f t="shared" si="0"/>
         <v>45683</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="9">
         <f>(C27 * Prices!D26) / $E27</f>
         <v>0.51239669421487588</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <f>(D27 * Prices!E26) / E27</f>
         <v>0.48760330578512406</v>
       </c>
@@ -2216,63 +1879,39 @@
         <f xml:space="preserve"> $C28 * Prices!$D27 + $D28 * Prices!$E27</f>
         <v>0.95537190082644619</v>
       </c>
-      <c r="F28" s="10">
-        <f>(F27 * Prices!D26) / $H27</f>
-        <v>0.55357142857142827</v>
-      </c>
-      <c r="G28" s="10">
-        <f>(G27 * Prices!E26) / $H27</f>
-        <v>0.44642857142857167</v>
-      </c>
-      <c r="H28" s="7">
-        <f xml:space="preserve"> $F28 * Prices!$D27 + $G28 * Prices!$E27</f>
-        <v>0.95982142857142849</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45684</v>
       </c>
-      <c r="B29" s="13">
-        <f>A29</f>
+      <c r="B29" s="12">
+        <f t="shared" si="0"/>
         <v>45684</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="8">
         <v>0.5</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>0.5</v>
       </c>
       <c r="E29" s="7">
         <f xml:space="preserve"> $C29 * Prices!$D28 + $D29 * Prices!$E28</f>
         <v>1.0595555555555556</v>
       </c>
-      <c r="F29" s="10">
-        <f>(F28 * Prices!D27) / $H28</f>
-        <v>0.581395348837209</v>
-      </c>
-      <c r="G29" s="10">
-        <f>(G28 * Prices!E27) / $H28</f>
-        <v>0.418604651162791</v>
-      </c>
-      <c r="H29" s="7">
-        <f xml:space="preserve"> $F29 * Prices!$D28 + $G29 * Prices!$E28</f>
-        <v>1.0511627906976744</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45685</v>
       </c>
-      <c r="B30" s="12">
-        <f>A30</f>
+      <c r="B30" s="11">
+        <f t="shared" si="0"/>
         <v>45685</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="9">
         <f>(C29 * Prices!D28) / $E29</f>
         <v>0.47567114093959728</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <f>(D29 * Prices!E28) / E29</f>
         <v>0.52432885906040272</v>
       </c>
@@ -2280,32 +1919,20 @@
         <f xml:space="preserve"> $C30 * Prices!$D29 + $D30 * Prices!$E29</f>
         <v>0.95134228187919456</v>
       </c>
-      <c r="F30" s="10">
-        <f>(F29 * Prices!D28) / $H29</f>
-        <v>0.55752212389380507</v>
-      </c>
-      <c r="G30" s="10">
-        <f>(G29 * Prices!E28) / $H29</f>
-        <v>0.44247787610619504</v>
-      </c>
-      <c r="H30" s="7">
-        <f xml:space="preserve"> $F30 * Prices!$D29 + $G30 * Prices!$E29</f>
-        <v>0.96017699115044253</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45686</v>
       </c>
-      <c r="B31" s="12">
-        <f>A31</f>
+      <c r="B31" s="11">
+        <f t="shared" si="0"/>
         <v>45686</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <f>(C30 * Prices!D29) / $E30</f>
         <v>0.50396825396825395</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <f>(D30 * Prices!E29) / E30</f>
         <v>0.4960317460317461</v>
       </c>
@@ -2313,32 +1940,20 @@
         <f xml:space="preserve"> $C31 * Prices!$D30 + $D31 * Prices!$E30</f>
         <v>1.0590828924162259</v>
       </c>
-      <c r="F31" s="10">
-        <f>(F30 * Prices!D29) / $H30</f>
-        <v>0.58525345622119784</v>
-      </c>
-      <c r="G31" s="10">
-        <f>(G30 * Prices!E29) / $H30</f>
-        <v>0.41474654377880216</v>
-      </c>
-      <c r="H31" s="7">
-        <f xml:space="preserve"> $F31 * Prices!$D30 + $G31 * Prices!$E30</f>
-        <v>1.0506912442396314</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45687</v>
       </c>
-      <c r="B32" s="12">
-        <f>A32</f>
+      <c r="B32" s="11">
+        <f t="shared" si="0"/>
         <v>45687</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <f>(C31 * Prices!D30) / $E31</f>
         <v>0.47960033305578675</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <f>(D31 * Prices!E30) / E31</f>
         <v>0.52039966694421314</v>
       </c>
@@ -2346,32 +1961,20 @@
         <f xml:space="preserve"> $C32 * Prices!$D31 + $D32 * Prices!$E31</f>
         <v>0.95170691090757686</v>
       </c>
-      <c r="F32" s="10">
-        <f>(F31 * Prices!D30) / $H31</f>
-        <v>0.56140350877192946</v>
-      </c>
-      <c r="G32" s="10">
-        <f>(G31 * Prices!E30) / $H31</f>
-        <v>0.43859649122807048</v>
-      </c>
-      <c r="H32" s="7">
-        <f xml:space="preserve"> $F32 * Prices!$D31 + $G32 * Prices!$E31</f>
-        <v>0.96052631578947367</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45688</v>
       </c>
-      <c r="B33" s="12">
-        <f>A33</f>
+      <c r="B33" s="11">
+        <f t="shared" si="0"/>
         <v>45688</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="9">
         <f>(C32 * Prices!D31) / $E32</f>
         <v>0.50787401574803148</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <f>(D32 * Prices!E31) / E32</f>
         <v>0.49212598425196857</v>
       </c>
@@ -2379,48 +1982,26 @@
         <f xml:space="preserve"> $C33 * Prices!$D32 + $D33 * Prices!$E32</f>
         <v>1.0586176727909011</v>
       </c>
-      <c r="F33" s="10">
-        <f>(F32 * Prices!D31) / $H32</f>
-        <v>0.58904109589041065</v>
-      </c>
-      <c r="G33" s="10">
-        <f>(G32 * Prices!E31) / $H32</f>
-        <v>0.41095890410958935</v>
-      </c>
-      <c r="H33" s="7">
-        <f xml:space="preserve"> $F33 * Prices!$D32 + $G33 * Prices!$E32</f>
-        <v>1.0502283105022832</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>45689</v>
       </c>
-      <c r="B34" s="12">
-        <f>A34</f>
+      <c r="B34" s="11">
+        <f t="shared" si="0"/>
         <v>45689</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="9">
         <f>(C33 * Prices!D32) / $E33</f>
         <v>0.48347107438016529</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="9">
         <f>(D33 * Prices!E32) / E33</f>
         <v>0.51652892561983488</v>
       </c>
       <c r="E34" s="7">
         <f xml:space="preserve"> $C34 * Prices!$D33 + $D34 * Prices!$E33</f>
         <v>0.95206611570247945</v>
-      </c>
-      <c r="F34" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="G34" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="H34" s="7">
-        <f xml:space="preserve"> $F34 * Prices!$D33 + $G34 * Prices!$E33</f>
-        <v>0.95384615384615379</v>
       </c>
     </row>
   </sheetData>
@@ -2430,36 +2011,30 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B9E8070-11EC-4D5B-882F-63D06BDC939E}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.23046875" style="7"/>
+    <col min="2" max="2" width="9.23046875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>45658</v>
       </c>
       <c r="B2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45659</v>
       </c>
@@ -2467,12 +2042,8 @@
         <f>B2 * Expected_Weights!E4</f>
         <v>0.95500000000000007</v>
       </c>
-      <c r="C3" s="7">
-        <f>C2 * Expected_Weights!H4</f>
-        <v>0.95500000000000007</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45660</v>
       </c>
@@ -2480,12 +2051,8 @@
         <f>B3 * Expected_Weights!E5</f>
         <v>1.01</v>
       </c>
-      <c r="C4" s="7">
-        <f>C3 * Expected_Weights!H5</f>
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45661</v>
       </c>
@@ -2493,12 +2060,8 @@
         <f>B4 * Expected_Weights!E6</f>
         <v>0.96500000000000008</v>
       </c>
-      <c r="C5" s="7">
-        <f>C4 * Expected_Weights!H6</f>
-        <v>0.96500000000000008</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45662</v>
       </c>
@@ -2506,12 +2069,8 @@
         <f>B5 * Expected_Weights!E7</f>
         <v>1.0200000000000002</v>
       </c>
-      <c r="C6" s="7">
-        <f>C5 * Expected_Weights!H7</f>
-        <v>1.0200000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45663</v>
       </c>
@@ -2519,12 +2078,8 @@
         <f>B6 * Expected_Weights!E8</f>
         <v>0.97390384615384629</v>
       </c>
-      <c r="C7" s="7">
-        <f>C6 * Expected_Weights!H8</f>
-        <v>0.9750000000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45664</v>
       </c>
@@ -2532,12 +2087,8 @@
         <f>B7 * Expected_Weights!E9</f>
         <v>1.0298076923076924</v>
       </c>
-      <c r="C8" s="7">
-        <f>C7 * Expected_Weights!H9</f>
-        <v>1.0300000000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45665</v>
       </c>
@@ -2545,12 +2096,8 @@
         <f>B8 * Expected_Weights!E10</f>
         <v>0.98371153846153858</v>
       </c>
-      <c r="C9" s="7">
-        <f>C8 * Expected_Weights!H10</f>
-        <v>0.98500000000000054</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45666</v>
       </c>
@@ -2558,12 +2105,8 @@
         <f>B9 * Expected_Weights!E11</f>
         <v>1.0396153846153848</v>
       </c>
-      <c r="C10" s="7">
-        <f>C9 * Expected_Weights!H11</f>
-        <v>1.0400000000000005</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45667</v>
       </c>
@@ -2571,12 +2114,8 @@
         <f>B10 * Expected_Weights!E12</f>
         <v>0.99351923076923099</v>
       </c>
-      <c r="C11" s="7">
-        <f>C10 * Expected_Weights!H12</f>
-        <v>0.99500000000000044</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45668</v>
       </c>
@@ -2584,12 +2123,8 @@
         <f>B11 * Expected_Weights!E13</f>
         <v>1.049423076923077</v>
       </c>
-      <c r="C12" s="7">
-        <f>C11 * Expected_Weights!H13</f>
-        <v>1.0500000000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45669</v>
       </c>
@@ -2597,12 +2132,8 @@
         <f>B12 * Expected_Weights!E14</f>
         <v>1.0033269230769231</v>
       </c>
-      <c r="C13" s="7">
-        <f>C12 * Expected_Weights!H14</f>
-        <v>1.0050000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45670</v>
       </c>
@@ -2610,12 +2141,8 @@
         <f>B13 * Expected_Weights!E15</f>
         <v>1.0635867983367984</v>
       </c>
-      <c r="C14" s="7">
-        <f>C13 * Expected_Weights!H15</f>
-        <v>1.0600000000000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45671</v>
       </c>
@@ -2623,12 +2150,8 @@
         <f>B14 * Expected_Weights!E16</f>
         <v>1.0123659043659043</v>
       </c>
-      <c r="C15" s="7">
-        <f>C14 * Expected_Weights!H16</f>
-        <v>1.0150000000000003</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45672</v>
       </c>
@@ -2636,12 +2159,8 @@
         <f>B15 * Expected_Weights!E17</f>
         <v>1.0726257796257799</v>
       </c>
-      <c r="C16" s="7">
-        <f>C15 * Expected_Weights!H17</f>
-        <v>1.0700000000000005</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45673</v>
       </c>
@@ -2649,12 +2168,8 @@
         <f>B16 * Expected_Weights!E18</f>
         <v>1.0214048856548856</v>
       </c>
-      <c r="C17" s="7">
-        <f>C16 * Expected_Weights!H18</f>
-        <v>1.0250000000000006</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45674</v>
       </c>
@@ -2662,12 +2177,8 @@
         <f>B17 * Expected_Weights!E19</f>
         <v>1.0816647609147612</v>
       </c>
-      <c r="C18" s="7">
-        <f>C17 * Expected_Weights!H19</f>
-        <v>1.0800000000000007</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45675</v>
       </c>
@@ -2675,12 +2186,8 @@
         <f>B18 * Expected_Weights!E20</f>
         <v>1.0304438669438671</v>
       </c>
-      <c r="C19" s="7">
-        <f>C18 * Expected_Weights!H20</f>
-        <v>1.0350000000000008</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45676</v>
       </c>
@@ -2688,12 +2195,8 @@
         <f>B19 * Expected_Weights!E21</f>
         <v>1.0907037422037422</v>
       </c>
-      <c r="C20" s="7">
-        <f>C19 * Expected_Weights!H21</f>
-        <v>1.090000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45677</v>
       </c>
@@ -2701,12 +2204,8 @@
         <f>B20 * Expected_Weights!E22</f>
         <v>1.0407901811198421</v>
       </c>
-      <c r="C21" s="7">
-        <f>C20 * Expected_Weights!H22</f>
-        <v>1.045000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45678</v>
       </c>
@@ -2714,12 +2213,8 @@
         <f>B21 * Expected_Weights!E23</f>
         <v>1.0999469942563165</v>
       </c>
-      <c r="C22" s="7">
-        <f>C21 * Expected_Weights!H23</f>
-        <v>1.1000000000000012</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45679</v>
       </c>
@@ -2727,12 +2222,8 @@
         <f>B22 * Expected_Weights!E24</f>
         <v>1.0500334331724162</v>
       </c>
-      <c r="C23" s="7">
-        <f>C22 * Expected_Weights!H24</f>
-        <v>1.055000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45680</v>
       </c>
@@ -2740,12 +2231,8 @@
         <f>B23 * Expected_Weights!E25</f>
         <v>1.1091902463088905</v>
       </c>
-      <c r="C24" s="7">
-        <f>C23 * Expected_Weights!H25</f>
-        <v>1.110000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45681</v>
       </c>
@@ -2753,12 +2240,8 @@
         <f>B24 * Expected_Weights!E26</f>
         <v>1.0592766852249904</v>
       </c>
-      <c r="C25" s="7">
-        <f>C24 * Expected_Weights!H26</f>
-        <v>1.0650000000000008</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45682</v>
       </c>
@@ -2766,12 +2249,8 @@
         <f>B25 * Expected_Weights!E27</f>
         <v>1.1184334983614646</v>
       </c>
-      <c r="C26" s="7">
-        <f>C25 * Expected_Weights!H27</f>
-        <v>1.120000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45683</v>
       </c>
@@ -2779,12 +2258,8 @@
         <f>B26 * Expected_Weights!E28</f>
         <v>1.0685199372775644</v>
       </c>
-      <c r="C27" s="7">
-        <f>C26 * Expected_Weights!H28</f>
-        <v>1.0750000000000008</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45684</v>
       </c>
@@ -2792,12 +2267,8 @@
         <f>B27 * Expected_Weights!E29</f>
         <v>1.1321562357643171</v>
       </c>
-      <c r="C28" s="7">
-        <f>C27 * Expected_Weights!H29</f>
-        <v>1.1300000000000008</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45685</v>
       </c>
@@ -2805,12 +2276,8 @@
         <f>B28 * Expected_Weights!E30</f>
         <v>1.0770680967757849</v>
       </c>
-      <c r="C29" s="7">
-        <f>C28 * Expected_Weights!H30</f>
-        <v>1.0850000000000009</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45686</v>
       </c>
@@ -2818,12 +2285,8 @@
         <f>B29 * Expected_Weights!E31</f>
         <v>1.1407043952625378</v>
       </c>
-      <c r="C30" s="7">
-        <f>C29 * Expected_Weights!H31</f>
-        <v>1.140000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45687</v>
       </c>
@@ -2831,12 +2294,8 @@
         <f>B30 * Expected_Weights!E32</f>
         <v>1.0856162562740053</v>
       </c>
-      <c r="C31" s="7">
-        <f>C30 * Expected_Weights!H32</f>
-        <v>1.0950000000000009</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45688</v>
       </c>
@@ -2844,22 +2303,14 @@
         <f>B31 * Expected_Weights!E33</f>
         <v>1.1492525547607579</v>
       </c>
-      <c r="C32" s="7">
-        <f>C31 * Expected_Weights!H33</f>
-        <v>1.150000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45689</v>
       </c>
       <c r="B33" s="7">
         <f>B32 * Expected_Weights!E34</f>
         <v>1.0941644157722259</v>
-      </c>
-      <c r="C33" s="7">
-        <f>C32 * Expected_Weights!H34</f>
-        <v>1.0969230769230778</v>
       </c>
     </row>
   </sheetData>
@@ -2869,7 +2320,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9C66B4-691D-4E6C-9B58-26BA46864B57}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.07421875" bestFit="1" customWidth="1"/>
@@ -2889,40 +2340,40 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="N1" s="1"/>
     </row>
@@ -2936,11 +2387,11 @@
       <c r="C2" s="2">
         <v>45689</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>36</v>
+      <c r="D2" t="s">
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" s="5">
         <v>9.42</v>
@@ -2964,48 +2415,7 @@
         <v>-4.5999999999999996</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2">
-        <v>45658</v>
-      </c>
-      <c r="C3" s="2">
-        <v>45689</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
         <v>30</v>
-      </c>
-      <c r="F3" s="5">
-        <v>9.69</v>
-      </c>
-      <c r="G3" s="5">
-        <v>197.42</v>
-      </c>
-      <c r="H3" s="5">
-        <v>75.959999999999994</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1.32</v>
-      </c>
-      <c r="J3">
-        <v>2.12</v>
-      </c>
-      <c r="K3" s="5">
-        <v>-4.62</v>
-      </c>
-      <c r="L3" s="5">
-        <v>-4.24</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_rb_sigma.xlsx
+++ b/public/tests/data/test_rb_sigma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECB37A3-B6A9-4174-ADAE-FE4806820B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959CAA9B-6404-469C-9668-121A3FE49D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>Name</t>
   </si>
@@ -129,9 +129,6 @@
   </si>
   <si>
     <t>Max Drawdown Period</t>
-  </si>
-  <si>
-    <t>full</t>
   </si>
   <si>
     <t>1 days</t>
@@ -555,7 +552,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -563,7 +560,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -631,10 +628,10 @@
         <v>9</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>36</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
@@ -1266,18 +1263,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -1303,7 +1300,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EA1201-9593-4FA8-BE4A-D6543E3F5A5B}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
@@ -1311,12 +1308,12 @@
     <col min="5" max="5" width="11.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>14</v>
@@ -1325,15 +1322,15 @@
         <v>14</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>8</v>
@@ -1342,10 +1339,10 @@
         <v>9</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45658</v>
       </c>
@@ -1363,7 +1360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45659</v>
       </c>
@@ -1382,7 +1379,7 @@
         <v>0.95500000000000007</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45660</v>
       </c>
@@ -1403,7 +1400,7 @@
         <v>1.0575916230366491</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45661</v>
       </c>
@@ -1424,7 +1421,7 @@
         <v>0.95544554455445552</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45662</v>
       </c>
@@ -1445,7 +1442,7 @@
         <v>1.0569948186528499</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45663</v>
       </c>
@@ -1453,18 +1450,20 @@
         <f t="shared" si="0"/>
         <v>45663</v>
       </c>
-      <c r="C8" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.5</v>
+      <c r="C8" s="9">
+        <f>(C7 * Prices!D6) / $E7</f>
+        <v>0.50980392156862742</v>
+      </c>
+      <c r="D8" s="9">
+        <f>(D7 * Prices!E6) / E7</f>
+        <v>0.49019607843137253</v>
       </c>
       <c r="E8" s="7">
         <f xml:space="preserve"> $C8 * Prices!$D7 + $D8 * Prices!$E7</f>
-        <v>0.95480769230769225</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.95588235294117641</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45664</v>
       </c>
@@ -1474,18 +1473,18 @@
       </c>
       <c r="C9" s="9">
         <f>(C8 * Prices!D7) / $E8</f>
-        <v>0.52870090634441091</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="D9" s="9">
         <f>(D8 * Prices!E7) / E8</f>
-        <v>0.47129909365558914</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="E9" s="7">
         <f xml:space="preserve"> $C9 * Prices!$D8 + $D9 * Prices!$E8</f>
-        <v>1.0574018126888218</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0564102564102564</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45665</v>
       </c>
@@ -1495,18 +1494,18 @@
       </c>
       <c r="C10" s="9">
         <f>(C9 * Prices!D8) / $E9</f>
-        <v>0.50476190476190474</v>
+        <v>0.5145631067961165</v>
       </c>
       <c r="D10" s="9">
         <f>(D9 * Prices!E8) / E9</f>
-        <v>0.4952380952380952</v>
+        <v>0.48543689320388356</v>
       </c>
       <c r="E10" s="7">
         <f xml:space="preserve"> $C10 * Prices!$D9 + $D10 * Prices!$E9</f>
-        <v>0.95523809523809522</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.95631067961165073</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45666</v>
       </c>
@@ -1516,18 +1515,18 @@
       </c>
       <c r="C11" s="9">
         <f>(C10 * Prices!D9) / $E10</f>
-        <v>0.53339980059820546</v>
+        <v>0.54314720812182737</v>
       </c>
       <c r="D11" s="9">
         <f>(D10 * Prices!E9) / E10</f>
-        <v>0.46660019940179459</v>
+        <v>0.45685279187817257</v>
       </c>
       <c r="E11" s="7">
         <f xml:space="preserve"> $C11 * Prices!$D10 + $D11 * Prices!$E10</f>
-        <v>1.0568295114656032</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0558375634517765</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45667</v>
       </c>
@@ -1537,18 +1536,18 @@
       </c>
       <c r="C12" s="9">
         <f>(C11 * Prices!D10) / $E11</f>
-        <v>0.50943396226415094</v>
+        <v>0.51923076923076916</v>
       </c>
       <c r="D12" s="9">
         <f>(D11 * Prices!E10) / E11</f>
-        <v>0.49056603773584906</v>
+        <v>0.48076923076923084</v>
       </c>
       <c r="E12" s="7">
         <f xml:space="preserve"> $C12 * Prices!$D11 + $D12 * Prices!$E11</f>
-        <v>0.95566037735849063</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.95673076923076916</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45668</v>
       </c>
@@ -1558,18 +1557,18 @@
       </c>
       <c r="C13" s="9">
         <f>(C12 * Prices!D11) / $E12</f>
-        <v>0.53800592300098715</v>
+        <v>0.54773869346733661</v>
       </c>
       <c r="D13" s="9">
         <f>(D12 * Prices!E11) / E12</f>
-        <v>0.46199407699901279</v>
+        <v>0.45226130653266344</v>
       </c>
       <c r="E13" s="7">
         <f xml:space="preserve"> $C13 * Prices!$D12 + $D13 * Prices!$E12</f>
-        <v>1.0562685093780848</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0552763819095479</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45669</v>
       </c>
@@ -1579,18 +1578,18 @@
       </c>
       <c r="C14" s="9">
         <f>(C13 * Prices!D12) / $E13</f>
-        <v>0.51401869158878499</v>
+        <v>0.52380952380952372</v>
       </c>
       <c r="D14" s="9">
         <f>(D13 * Prices!E12) / E13</f>
-        <v>0.48598130841121495</v>
+        <v>0.47619047619047628</v>
       </c>
       <c r="E14" s="7">
         <f xml:space="preserve"> $C14 * Prices!$D13 + $D14 * Prices!$E13</f>
-        <v>0.9560747663551401</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.95714285714285707</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45670</v>
       </c>
@@ -1599,17 +1598,18 @@
         <v>45670</v>
       </c>
       <c r="C15" s="8">
-        <v>0.5</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="D15" s="8">
-        <v>0.5</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="E15" s="7">
         <f xml:space="preserve"> $C15 * Prices!$D14 + $D15 * Prices!$E14</f>
-        <v>1.06006006006006</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0575075075075075</v>
+      </c>
+      <c r="G15" s="9"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45671</v>
       </c>
@@ -1619,18 +1619,18 @@
       </c>
       <c r="C16" s="9">
         <f>(C15 * Prices!D14) / $E15</f>
-        <v>0.47592067988668552</v>
+        <v>0.50092290217236979</v>
       </c>
       <c r="D16" s="9">
         <f>(D15 * Prices!E14) / E15</f>
-        <v>0.52407932011331448</v>
+        <v>0.49907709782763027</v>
       </c>
       <c r="E16" s="7">
         <f xml:space="preserve"> $C16 * Prices!$D15 + $D16 * Prices!$E15</f>
-        <v>0.95184135977337103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.9545648161294904</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45672</v>
       </c>
@@ -1640,18 +1640,18 @@
       </c>
       <c r="C17" s="9">
         <f>(C16 * Prices!D15) / $E16</f>
-        <v>0.5044642857142857</v>
+        <v>0.52945113788487286</v>
       </c>
       <c r="D17" s="9">
         <f>(D16 * Prices!E15) / E16</f>
-        <v>0.49553571428571436</v>
+        <v>0.47054886211512709</v>
       </c>
       <c r="E17" s="7">
         <f xml:space="preserve"> $C17 * Prices!$D16 + $D17 * Prices!$E16</f>
-        <v>1.0595238095238098</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0569686152015469</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45673</v>
       </c>
@@ -1661,18 +1661,18 @@
       </c>
       <c r="C18" s="9">
         <f>(C17 * Prices!D16) / $E17</f>
-        <v>0.48033707865168523</v>
+        <v>0.50534759358288783</v>
       </c>
       <c r="D18" s="9">
         <f>(D17 * Prices!E16) / E17</f>
-        <v>0.5196629213483146</v>
+        <v>0.49465240641711222</v>
       </c>
       <c r="E18" s="7">
         <f xml:space="preserve"> $C18 * Prices!$D17 + $D18 * Prices!$E17</f>
-        <v>0.95224719101123578</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.9549676329862089</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45674</v>
       </c>
@@ -1682,18 +1682,18 @@
       </c>
       <c r="C19" s="9">
         <f>(C18 * Prices!D17) / $E18</f>
-        <v>0.50884955752212391</v>
+        <v>0.53381962864721499</v>
       </c>
       <c r="D19" s="9">
         <f>(D18 * Prices!E17) / E18</f>
-        <v>0.4911504424778762</v>
+        <v>0.46618037135278506</v>
       </c>
       <c r="E19" s="7">
         <f xml:space="preserve"> $C19 * Prices!$D18 + $D19 * Prices!$E18</f>
-        <v>1.0589970501474928</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0564397288535221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45675</v>
       </c>
@@ -1703,18 +1703,18 @@
       </c>
       <c r="C20" s="9">
         <f>(C19 * Prices!D18) / $E19</f>
-        <v>0.48467966573816151</v>
+        <v>0.50969451806388621</v>
       </c>
       <c r="D20" s="9">
         <f>(D19 * Prices!E18) / E19</f>
-        <v>0.51532033426183854</v>
+        <v>0.49030548193611373</v>
       </c>
       <c r="E20" s="7">
         <f xml:space="preserve"> $C20 * Prices!$D19 + $D20 * Prices!$E19</f>
-        <v>0.9526462395543176</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.95536337006556005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45676</v>
       </c>
@@ -1724,18 +1724,18 @@
       </c>
       <c r="C21" s="9">
         <f>(C20 * Prices!D19) / $E20</f>
-        <v>0.51315789473684204</v>
+        <v>0.53810775295663604</v>
       </c>
       <c r="D21" s="9">
         <f>(D20 * Prices!E19) / E20</f>
-        <v>0.48684210526315796</v>
+        <v>0.4618922470433639</v>
       </c>
       <c r="E21" s="7">
         <f xml:space="preserve"> $C21 * Prices!$D20 + $D21 * Prices!$E20</f>
-        <v>1.0584795321637426</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0559205723463279</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45677</v>
       </c>
@@ -1743,18 +1743,20 @@
         <f t="shared" si="0"/>
         <v>45677</v>
       </c>
-      <c r="C22" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D22" s="8">
-        <v>0.5</v>
+      <c r="C22" s="9">
+        <f>(C21 * Prices!D20) / $E21</f>
+        <v>0.51396570796460184</v>
+      </c>
+      <c r="D22" s="9">
+        <f>(D21 * Prices!E20) / E21</f>
+        <v>0.48603429203539822</v>
       </c>
       <c r="E22" s="7">
         <f xml:space="preserve"> $C22 * Prices!$D21 + $D22 * Prices!$E21</f>
-        <v>0.95423728813559316</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.95575221238938057</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45678</v>
       </c>
@@ -1764,18 +1766,18 @@
       </c>
       <c r="C23" s="9">
         <f>(C22 * Prices!D21) / $E22</f>
-        <v>0.52841918294849022</v>
+        <v>0.54231770833333337</v>
       </c>
       <c r="D23" s="9">
         <f>(D22 * Prices!E21) / E22</f>
-        <v>0.47158081705150978</v>
+        <v>0.45768229166666663</v>
       </c>
       <c r="E23" s="7">
         <f xml:space="preserve"> $C23 * Prices!$D22 + $D23 * Prices!$E22</f>
-        <v>1.0568383658969807</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0554108796296298</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45679</v>
       </c>
@@ -1785,18 +1787,18 @@
       </c>
       <c r="C24" s="9">
         <f>(C23 * Prices!D22) / $E23</f>
-        <v>0.50420168067226878</v>
+        <v>0.5181631254283755</v>
       </c>
       <c r="D24" s="9">
         <f>(D23 * Prices!E22) / E23</f>
-        <v>0.49579831932773105</v>
+        <v>0.48183687457162439</v>
       </c>
       <c r="E24" s="7">
         <f xml:space="preserve"> $C24 * Prices!$D23 + $D24 * Prices!$E23</f>
-        <v>0.95462184873949563</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.95613433858807384</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45680</v>
       </c>
@@ -1806,18 +1808,18 @@
       </c>
       <c r="C25" s="9">
         <f>(C24 * Prices!D23) / $E24</f>
-        <v>0.53257042253521125</v>
+        <v>0.54645161290322586</v>
       </c>
       <c r="D25" s="9">
         <f>(D24 * Prices!E23) / E24</f>
-        <v>0.4674295774647888</v>
+        <v>0.45354838709677425</v>
       </c>
       <c r="E25" s="7">
         <f xml:space="preserve"> $C25 * Prices!$D24 + $D25 * Prices!$E24</f>
-        <v>1.0563380281690142</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0549103942652331</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45681</v>
       </c>
@@ -1827,18 +1829,18 @@
       </c>
       <c r="C26" s="9">
         <f>(C25 * Prices!D24) / $E25</f>
-        <v>0.5083333333333333</v>
+        <v>0.52228866539820595</v>
       </c>
       <c r="D26" s="9">
         <f>(D25 * Prices!E24) / E25</f>
-        <v>0.49166666666666675</v>
+        <v>0.47771133460179399</v>
       </c>
       <c r="E26" s="7">
         <f xml:space="preserve"> $C26 * Prices!$D25 + $D26 * Prices!$E25</f>
-        <v>0.95500000000000007</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.95650992117423195</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45682</v>
       </c>
@@ -1848,18 +1850,18 @@
       </c>
       <c r="C27" s="9">
         <f>(C26 * Prices!D25) / $E26</f>
-        <v>0.53664921465968574</v>
+        <v>0.55051150895140655</v>
       </c>
       <c r="D27" s="9">
         <f>(D26 * Prices!E25) / E26</f>
-        <v>0.46335078534031415</v>
+        <v>0.44948849104859345</v>
       </c>
       <c r="E27" s="7">
         <f xml:space="preserve"> $C27 * Prices!$D26 + $D27 * Prices!$E26</f>
-        <v>1.0558464223385688</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0544188689968741</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45683</v>
       </c>
@@ -1869,18 +1871,18 @@
       </c>
       <c r="C28" s="9">
         <f>(C27 * Prices!D26) / $E27</f>
-        <v>0.51239669421487588</v>
+        <v>0.5263441584692089</v>
       </c>
       <c r="D28" s="9">
         <f>(D27 * Prices!E26) / E27</f>
-        <v>0.48760330578512406</v>
+        <v>0.47365584153079116</v>
       </c>
       <c r="E28" s="7">
         <f xml:space="preserve"> $C28 * Prices!$D27 + $D28 * Prices!$E27</f>
-        <v>0.95537190082644619</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.95687912680231779</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45684</v>
       </c>
@@ -1889,17 +1891,18 @@
         <v>45684</v>
       </c>
       <c r="C29" s="8">
-        <v>0.5</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="D29" s="8">
-        <v>0.5</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="E29" s="7">
         <f xml:space="preserve"> $C29 * Prices!$D28 + $D29 * Prices!$E28</f>
-        <v>1.0595555555555556</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0569777777777778</v>
+      </c>
+      <c r="G29" s="9"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45685</v>
       </c>
@@ -1909,18 +1912,18 @@
       </c>
       <c r="C30" s="9">
         <f>(C29 * Prices!D28) / $E29</f>
-        <v>0.47567114093959728</v>
+        <v>0.50067277773105712</v>
       </c>
       <c r="D30" s="9">
         <f>(D29 * Prices!E28) / E29</f>
-        <v>0.52432885906040272</v>
+        <v>0.49932722226894288</v>
       </c>
       <c r="E30" s="7">
         <f xml:space="preserve"> $C30 * Prices!$D29 + $D30 * Prices!$E29</f>
-        <v>0.95134228187919456</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+        <v>0.95404087124716175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45686</v>
       </c>
@@ -1930,18 +1933,18 @@
       </c>
       <c r="C31" s="9">
         <f>(C30 * Prices!D29) / $E30</f>
-        <v>0.50396825396825395</v>
+        <v>0.52895676318921059</v>
       </c>
       <c r="D31" s="9">
         <f>(D30 * Prices!E29) / E30</f>
-        <v>0.4960317460317461</v>
+        <v>0.47104323681078936</v>
       </c>
       <c r="E31" s="7">
         <f xml:space="preserve"> $C31 * Prices!$D30 + $D31 * Prices!$E30</f>
-        <v>1.0590828924162259</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+        <v>1.0565031513068006</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45687</v>
       </c>
@@ -1951,15 +1954,15 @@
       </c>
       <c r="C32" s="9">
         <f>(C31 * Prices!D30) / $E31</f>
-        <v>0.47960033305578675</v>
+        <v>0.504609736765258</v>
       </c>
       <c r="D32" s="9">
         <f>(D31 * Prices!E30) / E31</f>
-        <v>0.52039966694421314</v>
+        <v>0.49539026323474195</v>
       </c>
       <c r="E32" s="7">
         <f xml:space="preserve"> $C32 * Prices!$D31 + $D32 * Prices!$E31</f>
-        <v>0.95170691090757686</v>
+        <v>0.95440323724500442</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
@@ -1972,15 +1975,15 @@
       </c>
       <c r="C33" s="9">
         <f>(C32 * Prices!D31) / $E32</f>
-        <v>0.50787401574803148</v>
+        <v>0.53284815106215577</v>
       </c>
       <c r="D33" s="9">
         <f>(D32 * Prices!E31) / E32</f>
-        <v>0.49212598425196857</v>
+        <v>0.46715184893784417</v>
       </c>
       <c r="E33" s="7">
         <f xml:space="preserve"> $C33 * Prices!$D32 + $D33 * Prices!$E32</f>
-        <v>1.0586176727909011</v>
+        <v>1.056036366815281</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
@@ -1993,15 +1996,15 @@
       </c>
       <c r="C34" s="9">
         <f>(C33 * Prices!D32) / $E33</f>
-        <v>0.48347107438016529</v>
+        <v>0.50848509933774833</v>
       </c>
       <c r="D34" s="9">
         <f>(D33 * Prices!E32) / E33</f>
-        <v>0.51652892561983488</v>
+        <v>0.49151490066225162</v>
       </c>
       <c r="E34" s="7">
         <f xml:space="preserve"> $C34 * Prices!$D33 + $D34 * Prices!$E33</f>
-        <v>0.95206611570247945</v>
+        <v>0.95475993377483437</v>
       </c>
     </row>
   </sheetData>
@@ -2076,7 +2079,7 @@
       </c>
       <c r="B7" s="7">
         <f>B6 * Expected_Weights!E8</f>
-        <v>0.97390384615384629</v>
+        <v>0.9750000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
@@ -2085,7 +2088,7 @@
       </c>
       <c r="B8" s="7">
         <f>B7 * Expected_Weights!E9</f>
-        <v>1.0298076923076924</v>
+        <v>1.0300000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
@@ -2094,7 +2097,7 @@
       </c>
       <c r="B9" s="7">
         <f>B8 * Expected_Weights!E10</f>
-        <v>0.98371153846153858</v>
+        <v>0.98500000000000054</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
@@ -2103,7 +2106,7 @@
       </c>
       <c r="B10" s="7">
         <f>B9 * Expected_Weights!E11</f>
-        <v>1.0396153846153848</v>
+        <v>1.0400000000000005</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
@@ -2112,7 +2115,7 @@
       </c>
       <c r="B11" s="7">
         <f>B10 * Expected_Weights!E12</f>
-        <v>0.99351923076923099</v>
+        <v>0.99500000000000044</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
@@ -2121,7 +2124,7 @@
       </c>
       <c r="B12" s="7">
         <f>B11 * Expected_Weights!E13</f>
-        <v>1.049423076923077</v>
+        <v>1.0500000000000005</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
@@ -2130,7 +2133,7 @@
       </c>
       <c r="B13" s="7">
         <f>B12 * Expected_Weights!E14</f>
-        <v>1.0033269230769231</v>
+        <v>1.0050000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
@@ -2139,7 +2142,7 @@
       </c>
       <c r="B14" s="7">
         <f>B13 * Expected_Weights!E15</f>
-        <v>1.0635867983367984</v>
+        <v>1.0627950450450454</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
@@ -2148,7 +2151,7 @@
       </c>
       <c r="B15" s="7">
         <f>B14 * Expected_Weights!E16</f>
-        <v>1.0123659043659043</v>
+        <v>1.0145067567567572</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
@@ -2157,7 +2160,7 @@
       </c>
       <c r="B16" s="7">
         <f>B15 * Expected_Weights!E17</f>
-        <v>1.0726257796257799</v>
+        <v>1.0723018018018022</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
@@ -2166,7 +2169,7 @@
       </c>
       <c r="B17" s="7">
         <f>B16 * Expected_Weights!E18</f>
-        <v>1.0214048856548856</v>
+        <v>1.024013513513514</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
@@ -2175,7 +2178,7 @@
       </c>
       <c r="B18" s="7">
         <f>B17 * Expected_Weights!E19</f>
-        <v>1.0816647609147612</v>
+        <v>1.0818085585585593</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
@@ -2184,7 +2187,7 @@
       </c>
       <c r="B19" s="7">
         <f>B18 * Expected_Weights!E20</f>
-        <v>1.0304438669438671</v>
+        <v>1.033520270270271</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
@@ -2193,7 +2196,7 @@
       </c>
       <c r="B20" s="7">
         <f>B19 * Expected_Weights!E21</f>
-        <v>1.0907037422037422</v>
+        <v>1.0913153153153161</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
@@ -2202,7 +2205,7 @@
       </c>
       <c r="B21" s="7">
         <f>B20 * Expected_Weights!E22</f>
-        <v>1.0407901811198421</v>
+        <v>1.0430270270270279</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
@@ -2211,7 +2214,7 @@
       </c>
       <c r="B22" s="7">
         <f>B21 * Expected_Weights!E23</f>
-        <v>1.0999469942563165</v>
+        <v>1.1008220720720732</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
@@ -2220,7 +2223,7 @@
       </c>
       <c r="B23" s="7">
         <f>B22 * Expected_Weights!E24</f>
-        <v>1.0500334331724162</v>
+        <v>1.0525337837837847</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
@@ -2229,7 +2232,7 @@
       </c>
       <c r="B24" s="7">
         <f>B23 * Expected_Weights!E25</f>
-        <v>1.1091902463088905</v>
+        <v>1.11032882882883</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
@@ -2238,7 +2241,7 @@
       </c>
       <c r="B25" s="7">
         <f>B24 * Expected_Weights!E26</f>
-        <v>1.0592766852249904</v>
+        <v>1.0620405405405415</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
@@ -2247,7 +2250,7 @@
       </c>
       <c r="B26" s="7">
         <f>B25 * Expected_Weights!E27</f>
-        <v>1.1184334983614646</v>
+        <v>1.1198355855855866</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
@@ -2256,7 +2259,7 @@
       </c>
       <c r="B27" s="7">
         <f>B26 * Expected_Weights!E28</f>
-        <v>1.0685199372775644</v>
+        <v>1.0715472972972984</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
@@ -2265,7 +2268,7 @@
       </c>
       <c r="B28" s="7">
         <f>B27 * Expected_Weights!E29</f>
-        <v>1.1321562357643171</v>
+        <v>1.1326016810810822</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
@@ -2274,7 +2277,7 @@
       </c>
       <c r="B29" s="7">
         <f>B28 * Expected_Weights!E30</f>
-        <v>1.0770680967757849</v>
+        <v>1.0805482945945957</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
@@ -2283,7 +2286,7 @@
       </c>
       <c r="B30" s="7">
         <f>B29 * Expected_Weights!E31</f>
-        <v>1.1407043952625378</v>
+        <v>1.1416026783783795</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
@@ -2292,7 +2295,7 @@
       </c>
       <c r="B31" s="7">
         <f>B30 * Expected_Weights!E32</f>
-        <v>1.0856162562740053</v>
+        <v>1.089549291891893</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
@@ -2301,7 +2304,7 @@
       </c>
       <c r="B32" s="7">
         <f>B31 * Expected_Weights!E33</f>
-        <v>1.1492525547607579</v>
+        <v>1.1506036756756768</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.4">
@@ -2310,7 +2313,7 @@
       </c>
       <c r="B33" s="7">
         <f>B32 * Expected_Weights!E34</f>
-        <v>1.0941644157722259</v>
+        <v>1.0985502891891901</v>
       </c>
     </row>
   </sheetData>
@@ -2388,34 +2391,34 @@
         <v>45689</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="5">
+        <v>9.86</v>
+      </c>
+      <c r="G2" s="5">
+        <v>202.66</v>
+      </c>
+      <c r="H2" s="5">
+        <v>79.42</v>
+      </c>
+      <c r="I2" s="5">
+        <v>1.31</v>
+      </c>
+      <c r="J2">
+        <v>2.1</v>
+      </c>
+      <c r="K2" s="5">
+        <v>-4.5999999999999996</v>
+      </c>
+      <c r="L2" s="5">
+        <v>-4.4400000000000004</v>
+      </c>
+      <c r="M2" t="s">
         <v>29</v>
-      </c>
-      <c r="F2" s="5">
-        <v>9.42</v>
-      </c>
-      <c r="G2" s="5">
-        <v>188.72</v>
-      </c>
-      <c r="H2" s="5">
-        <v>82.08</v>
-      </c>
-      <c r="I2" s="5">
-        <v>1.26</v>
-      </c>
-      <c r="J2">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="K2" s="5">
-        <v>-4.87</v>
-      </c>
-      <c r="L2" s="5">
-        <v>-4.5999999999999996</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_rb_sigma.xlsx
+++ b/public/tests/data/test_rb_sigma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959CAA9B-6404-469C-9668-121A3FE49D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8552B4B5-037A-4B44-A160-540283F1776B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>Name</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>sigma</t>
+  </si>
+  <si>
+    <t>StdDev</t>
   </si>
 </sst>
 </file>
@@ -573,34 +576,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C271D88-DDEC-4A65-8905-A99CA73725FC}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C2" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_rb_sigma.xlsx
+++ b/public/tests/data/test_rb_sigma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8552B4B5-037A-4B44-A160-540283F1776B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB43F57-A5AF-48F0-BCC0-15E46E9C7003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
   <si>
     <t>Name</t>
   </si>
@@ -168,6 +168,33 @@
   </si>
   <si>
     <t>StdDev</t>
+  </si>
+  <si>
+    <t>_A3_grow</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>The third asset</t>
+  </si>
+  <si>
+    <t>_A1_unbal</t>
+  </si>
+  <si>
+    <t>_A2_unbal</t>
+  </si>
+  <si>
+    <t>_A3_unbal</t>
+  </si>
+  <si>
+    <t>_A1_lim</t>
+  </si>
+  <si>
+    <t>_A2_lim</t>
+  </si>
+  <si>
+    <t>_A3_lim</t>
   </si>
 </sst>
 </file>
@@ -179,7 +206,7 @@
     <numFmt numFmtId="165" formatCode="0.0000%"/>
     <numFmt numFmtId="166" formatCode="[$]dddd" x16r2:formatCode16="[$-en-SE]dddd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,6 +216,15 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -216,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -234,6 +270,9 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,13 +615,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C271D88-DDEC-4A65-8905-A99CA73725FC}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -592,8 +631,9 @@
       <c r="C1" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -604,7 +644,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -612,6 +652,17 @@
         <v>11</v>
       </c>
       <c r="C3" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="3">
         <v>0.1</v>
       </c>
     </row>
@@ -622,14 +673,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1942483-BB80-4E18-92F0-22F7848078C4}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.23046875" style="7"/>
+    <col min="5" max="5" width="9.23046875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -639,14 +690,20 @@
       <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G1" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>45658</v>
       </c>
@@ -656,14 +713,20 @@
       <c r="C2">
         <v>100</v>
       </c>
-      <c r="D2" s="7">
-        <v>0</v>
+      <c r="D2">
+        <v>200</v>
       </c>
       <c r="E2" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F2" s="7">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45659</v>
       </c>
@@ -673,16 +736,23 @@
       <c r="C3">
         <v>90</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3">
+        <v>199</v>
+      </c>
+      <c r="E3" s="7">
         <f>B3/B2</f>
         <v>1.01</v>
       </c>
-      <c r="E3" s="7">
+      <c r="F3" s="7">
         <f>C3/C2</f>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G3" s="7">
+        <f>D3/D2</f>
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45660</v>
       </c>
@@ -692,16 +762,23 @@
       <c r="C4">
         <v>100</v>
       </c>
-      <c r="D4" s="7">
-        <f t="shared" ref="D4:D10" si="0">B4/B3</f>
+      <c r="D4">
+        <v>198</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" ref="E4:E10" si="0">B4/B3</f>
         <v>1.0099009900990099</v>
       </c>
-      <c r="E4" s="7">
-        <f t="shared" ref="E4:E10" si="1">C4/C3</f>
+      <c r="F4" s="7">
+        <f t="shared" ref="F4:F10" si="1">C4/C3</f>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G4" s="7">
+        <f t="shared" ref="G4:G33" si="2">D4/D3</f>
+        <v>0.99497487437185927</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45661</v>
       </c>
@@ -711,16 +788,23 @@
       <c r="C5">
         <v>90</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5">
+        <v>197</v>
+      </c>
+      <c r="E5" s="7">
         <f t="shared" si="0"/>
         <v>1.0098039215686274</v>
       </c>
-      <c r="E5" s="7">
+      <c r="F5" s="7">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G5" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99494949494949492</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45662</v>
       </c>
@@ -730,16 +814,23 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6">
+        <v>196</v>
+      </c>
+      <c r="E6" s="7">
         <f t="shared" si="0"/>
         <v>1.0097087378640777</v>
       </c>
-      <c r="E6" s="7">
+      <c r="F6" s="7">
         <f t="shared" si="1"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G6" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99492385786802029</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45663</v>
       </c>
@@ -749,16 +840,23 @@
       <c r="C7">
         <v>90</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7">
+        <v>195</v>
+      </c>
+      <c r="E7" s="7">
         <f t="shared" si="0"/>
         <v>1.0096153846153846</v>
       </c>
-      <c r="E7" s="7">
+      <c r="F7" s="7">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G7" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99489795918367352</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45664</v>
       </c>
@@ -768,16 +866,23 @@
       <c r="C8">
         <v>100</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8">
+        <v>194</v>
+      </c>
+      <c r="E8" s="7">
         <f t="shared" si="0"/>
         <v>1.0095238095238095</v>
       </c>
-      <c r="E8" s="7">
+      <c r="F8" s="7">
         <f t="shared" si="1"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G8" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99487179487179489</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45665</v>
       </c>
@@ -787,16 +892,23 @@
       <c r="C9">
         <v>90</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9">
+        <v>193</v>
+      </c>
+      <c r="E9" s="7">
         <f t="shared" si="0"/>
         <v>1.0094339622641511</v>
       </c>
-      <c r="E9" s="7">
+      <c r="F9" s="7">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G9" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99484536082474229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45666</v>
       </c>
@@ -806,16 +918,23 @@
       <c r="C10">
         <v>100</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10">
+        <v>192</v>
+      </c>
+      <c r="E10" s="7">
         <f t="shared" si="0"/>
         <v>1.0093457943925233</v>
       </c>
-      <c r="E10" s="7">
+      <c r="F10" s="7">
         <f t="shared" si="1"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G10" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99481865284974091</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45667</v>
       </c>
@@ -825,16 +944,23 @@
       <c r="C11">
         <v>90</v>
       </c>
-      <c r="D11" s="7">
-        <f t="shared" ref="D11:D20" si="2">B11/B10</f>
+      <c r="D11">
+        <v>191</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" ref="E11:E20" si="3">B11/B10</f>
         <v>1.0092592592592593</v>
       </c>
-      <c r="E11" s="7">
-        <f t="shared" ref="E11:E20" si="3">C11/C10</f>
+      <c r="F11" s="7">
+        <f t="shared" ref="F11:F20" si="4">C11/C10</f>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G11" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99479166666666663</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45668</v>
       </c>
@@ -844,16 +970,23 @@
       <c r="C12">
         <v>100</v>
       </c>
-      <c r="D12" s="7">
-        <f t="shared" si="2"/>
-        <v>1.0091743119266054</v>
+      <c r="D12">
+        <v>190</v>
       </c>
       <c r="E12" s="7">
         <f t="shared" si="3"/>
+        <v>1.0091743119266054</v>
+      </c>
+      <c r="F12" s="7">
+        <f t="shared" si="4"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G12" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99476439790575921</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45669</v>
       </c>
@@ -863,16 +996,23 @@
       <c r="C13">
         <v>90</v>
       </c>
-      <c r="D13" s="7">
-        <f t="shared" si="2"/>
-        <v>1.009090909090909</v>
+      <c r="D13">
+        <v>189</v>
       </c>
       <c r="E13" s="7">
         <f t="shared" si="3"/>
+        <v>1.009090909090909</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="4"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G13" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99473684210526314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45670</v>
       </c>
@@ -882,16 +1022,23 @@
       <c r="C14">
         <v>100</v>
       </c>
-      <c r="D14" s="7">
-        <f t="shared" si="2"/>
-        <v>1.0090090090090089</v>
+      <c r="D14">
+        <v>188</v>
       </c>
       <c r="E14" s="7">
         <f t="shared" si="3"/>
+        <v>1.0090090090090089</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="4"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G14" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99470899470899465</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45671</v>
       </c>
@@ -901,16 +1048,23 @@
       <c r="C15">
         <v>90</v>
       </c>
-      <c r="D15" s="7">
-        <f t="shared" si="2"/>
-        <v>1.0089285714285714</v>
+      <c r="D15">
+        <v>187</v>
       </c>
       <c r="E15" s="7">
         <f t="shared" si="3"/>
+        <v>1.0089285714285714</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="4"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G15" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99468085106382975</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45672</v>
       </c>
@@ -920,16 +1074,23 @@
       <c r="C16">
         <v>100</v>
       </c>
-      <c r="D16" s="7">
-        <f t="shared" si="2"/>
-        <v>1.0088495575221239</v>
+      <c r="D16">
+        <v>186</v>
       </c>
       <c r="E16" s="7">
         <f t="shared" si="3"/>
+        <v>1.0088495575221239</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="4"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G16" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99465240641711228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45673</v>
       </c>
@@ -939,16 +1100,23 @@
       <c r="C17">
         <v>90</v>
       </c>
-      <c r="D17" s="7">
-        <f t="shared" si="2"/>
-        <v>1.0087719298245614</v>
+      <c r="D17">
+        <v>185</v>
       </c>
       <c r="E17" s="7">
         <f t="shared" si="3"/>
+        <v>1.0087719298245614</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="4"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G17" s="7">
+        <f t="shared" si="2"/>
+        <v>0.9946236559139785</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45674</v>
       </c>
@@ -958,16 +1126,23 @@
       <c r="C18">
         <v>100</v>
       </c>
-      <c r="D18" s="7">
-        <f t="shared" si="2"/>
-        <v>1.008695652173913</v>
+      <c r="D18">
+        <v>184</v>
       </c>
       <c r="E18" s="7">
         <f t="shared" si="3"/>
+        <v>1.008695652173913</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="4"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G18" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99459459459459465</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45675</v>
       </c>
@@ -977,16 +1152,23 @@
       <c r="C19">
         <v>90</v>
       </c>
-      <c r="D19" s="7">
-        <f t="shared" si="2"/>
-        <v>1.0086206896551724</v>
+      <c r="D19">
+        <v>183</v>
       </c>
       <c r="E19" s="7">
         <f t="shared" si="3"/>
+        <v>1.0086206896551724</v>
+      </c>
+      <c r="F19" s="7">
+        <f t="shared" si="4"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G19" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99456521739130432</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45676</v>
       </c>
@@ -996,16 +1178,23 @@
       <c r="C20">
         <v>100</v>
       </c>
-      <c r="D20" s="7">
-        <f t="shared" si="2"/>
-        <v>1.0085470085470085</v>
+      <c r="D20">
+        <v>182</v>
       </c>
       <c r="E20" s="7">
         <f t="shared" si="3"/>
+        <v>1.0085470085470085</v>
+      </c>
+      <c r="F20" s="7">
+        <f t="shared" si="4"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G20" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99453551912568305</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45677</v>
       </c>
@@ -1015,16 +1204,23 @@
       <c r="C21">
         <v>90</v>
       </c>
-      <c r="D21" s="7">
-        <f t="shared" ref="D21:D33" si="4">B21/B20</f>
+      <c r="D21">
+        <v>181</v>
+      </c>
+      <c r="E21" s="7">
+        <f t="shared" ref="E21:E33" si="5">B21/B20</f>
         <v>1.0084745762711864</v>
       </c>
-      <c r="E21" s="7">
-        <f t="shared" ref="E21:E33" si="5">C21/C20</f>
+      <c r="F21" s="7">
+        <f t="shared" ref="F21:F33" si="6">C21/C20</f>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G21" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99450549450549453</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45678</v>
       </c>
@@ -1034,16 +1230,23 @@
       <c r="C22">
         <v>100</v>
       </c>
-      <c r="D22" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0084033613445378</v>
+      <c r="D22">
+        <v>180</v>
       </c>
       <c r="E22" s="7">
         <f t="shared" si="5"/>
+        <v>1.0084033613445378</v>
+      </c>
+      <c r="F22" s="7">
+        <f t="shared" si="6"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G22" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99447513812154698</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45679</v>
       </c>
@@ -1053,16 +1256,23 @@
       <c r="C23">
         <v>90</v>
       </c>
-      <c r="D23" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0083333333333333</v>
+      <c r="D23">
+        <v>179</v>
       </c>
       <c r="E23" s="7">
         <f t="shared" si="5"/>
+        <v>1.0083333333333333</v>
+      </c>
+      <c r="F23" s="7">
+        <f t="shared" si="6"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G23" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99444444444444446</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45680</v>
       </c>
@@ -1072,16 +1282,23 @@
       <c r="C24">
         <v>100</v>
       </c>
-      <c r="D24" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0082644628099173</v>
+      <c r="D24">
+        <v>178</v>
       </c>
       <c r="E24" s="7">
         <f t="shared" si="5"/>
+        <v>1.0082644628099173</v>
+      </c>
+      <c r="F24" s="7">
+        <f t="shared" si="6"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G24" s="7">
+        <f t="shared" si="2"/>
+        <v>0.994413407821229</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45681</v>
       </c>
@@ -1091,16 +1308,23 @@
       <c r="C25">
         <v>90</v>
       </c>
-      <c r="D25" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0081967213114753</v>
+      <c r="D25">
+        <v>177</v>
       </c>
       <c r="E25" s="7">
         <f t="shared" si="5"/>
+        <v>1.0081967213114753</v>
+      </c>
+      <c r="F25" s="7">
+        <f t="shared" si="6"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G25" s="7">
+        <f t="shared" si="2"/>
+        <v>0.9943820224719101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45682</v>
       </c>
@@ -1110,16 +1334,23 @@
       <c r="C26">
         <v>100</v>
       </c>
-      <c r="D26" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0081300813008129</v>
+      <c r="D26">
+        <v>176</v>
       </c>
       <c r="E26" s="7">
         <f t="shared" si="5"/>
+        <v>1.0081300813008129</v>
+      </c>
+      <c r="F26" s="7">
+        <f t="shared" si="6"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G26" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99435028248587576</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45683</v>
       </c>
@@ -1129,16 +1360,23 @@
       <c r="C27">
         <v>90</v>
       </c>
-      <c r="D27" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0080645161290323</v>
+      <c r="D27">
+        <v>175</v>
       </c>
       <c r="E27" s="7">
         <f t="shared" si="5"/>
+        <v>1.0080645161290323</v>
+      </c>
+      <c r="F27" s="7">
+        <f t="shared" si="6"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G27" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99431818181818177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45684</v>
       </c>
@@ -1148,16 +1386,23 @@
       <c r="C28">
         <v>100</v>
       </c>
-      <c r="D28" s="7">
-        <f t="shared" si="4"/>
-        <v>1.008</v>
+      <c r="D28">
+        <v>174</v>
       </c>
       <c r="E28" s="7">
         <f t="shared" si="5"/>
+        <v>1.008</v>
+      </c>
+      <c r="F28" s="7">
+        <f t="shared" si="6"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G28" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99428571428571433</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45685</v>
       </c>
@@ -1167,16 +1412,23 @@
       <c r="C29">
         <v>90</v>
       </c>
-      <c r="D29" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0079365079365079</v>
+      <c r="D29">
+        <v>173</v>
       </c>
       <c r="E29" s="7">
         <f t="shared" si="5"/>
+        <v>1.0079365079365079</v>
+      </c>
+      <c r="F29" s="7">
+        <f t="shared" si="6"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G29" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99425287356321834</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45686</v>
       </c>
@@ -1186,16 +1438,23 @@
       <c r="C30">
         <v>100</v>
       </c>
-      <c r="D30" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0078740157480315</v>
+      <c r="D30">
+        <v>172</v>
       </c>
       <c r="E30" s="7">
         <f t="shared" si="5"/>
+        <v>1.0078740157480315</v>
+      </c>
+      <c r="F30" s="7">
+        <f t="shared" si="6"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G30" s="7">
+        <f t="shared" si="2"/>
+        <v>0.9942196531791907</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45687</v>
       </c>
@@ -1205,16 +1464,23 @@
       <c r="C31">
         <v>90</v>
       </c>
-      <c r="D31" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0078125</v>
+      <c r="D31">
+        <v>171</v>
       </c>
       <c r="E31" s="7">
         <f t="shared" si="5"/>
+        <v>1.0078125</v>
+      </c>
+      <c r="F31" s="7">
+        <f t="shared" si="6"/>
         <v>0.9</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G31" s="7">
+        <f t="shared" si="2"/>
+        <v>0.9941860465116279</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45688</v>
       </c>
@@ -1224,16 +1490,23 @@
       <c r="C32">
         <v>100</v>
       </c>
-      <c r="D32" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0077519379844961</v>
+      <c r="D32">
+        <v>170</v>
       </c>
       <c r="E32" s="7">
         <f t="shared" si="5"/>
+        <v>1.0077519379844961</v>
+      </c>
+      <c r="F32" s="7">
+        <f t="shared" si="6"/>
         <v>1.1111111111111112</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G32" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99415204678362568</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45689</v>
       </c>
@@ -1243,13 +1516,20 @@
       <c r="C33">
         <v>90</v>
       </c>
-      <c r="D33" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0076923076923077</v>
+      <c r="D33">
+        <v>169</v>
       </c>
       <c r="E33" s="7">
         <f t="shared" si="5"/>
+        <v>1.0076923076923077</v>
+      </c>
+      <c r="F33" s="7">
+        <f t="shared" si="6"/>
         <v>0.9</v>
+      </c>
+      <c r="G33" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99411764705882355</v>
       </c>
     </row>
   </sheetData>
@@ -1259,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955DA01E-A3C8-43F7-BE2B-2D20BB66CB4A}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.3046875" bestFit="1" customWidth="1"/>
@@ -1302,7 +1582,15 @@
         <v>9</v>
       </c>
       <c r="B5" s="3">
-        <v>0.5</v>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1312,15 +1600,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EA1201-9593-4FA8-BE4A-D6543E3F5A5B}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.4609375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.15234375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.15234375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.765625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1334,10 +1623,13 @@
         <v>14</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1351,10 +1643,31 @@
         <v>9</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45658</v>
       </c>
@@ -1366,13 +1679,40 @@
         <v>0.5</v>
       </c>
       <c r="D3" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="F3" s="7">
+        <v>1</v>
+      </c>
+      <c r="G3" s="9">
+        <f>C3</f>
         <v>0.5</v>
       </c>
-      <c r="E3" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H3" s="9">
+        <f>D3</f>
+        <v>0.25</v>
+      </c>
+      <c r="I3" s="9">
+        <f>E3</f>
+        <v>0.25</v>
+      </c>
+      <c r="J3" s="9">
+        <f>C3+C3*Assets!$C2</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K3" s="9">
+        <f>D3+D3*Assets!$C3</f>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="L3" s="9">
+        <f>E3+E3*Assets!$C4</f>
+        <v>0.27500000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45659</v>
       </c>
@@ -1384,14 +1724,41 @@
         <v>0.5</v>
       </c>
       <c r="D4" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="F4" s="7">
+        <f xml:space="preserve"> $C4 * Prices!$E3 + $D4 * Prices!$F3 + $E4 * Prices!$G3</f>
+        <v>0.97875000000000001</v>
+      </c>
+      <c r="G4" s="9">
+        <f>C4</f>
         <v>0.5</v>
       </c>
-      <c r="E4" s="7">
-        <f xml:space="preserve"> $C4 * Prices!$D3 + $D4 * Prices!$E3</f>
-        <v>0.95500000000000007</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H4" s="9">
+        <f>D4</f>
+        <v>0.25</v>
+      </c>
+      <c r="I4" s="9">
+        <f>E4</f>
+        <v>0.25</v>
+      </c>
+      <c r="J4" s="9">
+        <f>C4-C4*Assets!$C2</f>
+        <v>0.45</v>
+      </c>
+      <c r="K4" s="9">
+        <f>D4-D4*Assets!$C3</f>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="L4" s="9">
+        <f>E4-E4*Assets!$C4</f>
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45660</v>
       </c>
@@ -1400,19 +1767,35 @@
         <v>45660</v>
       </c>
       <c r="C5" s="9">
-        <f>(C4 * Prices!D3) / $E4</f>
-        <v>0.52879581151832455</v>
+        <f>(C4 * Prices!E3) / $F4</f>
+        <v>0.51596424010217112</v>
       </c>
       <c r="D5" s="9">
-        <f>(D4 * Prices!E3) / $E4</f>
-        <v>0.47120418848167539</v>
-      </c>
-      <c r="E5" s="7">
-        <f xml:space="preserve"> $C5 * Prices!$D4 + $D5 * Prices!$E4</f>
-        <v>1.0575916230366491</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D4 * Prices!F3) / $F4</f>
+        <v>0.22988505747126436</v>
+      </c>
+      <c r="E5" s="9">
+        <f>(E4 * Prices!G3) / $F4</f>
+        <v>0.25415070242656451</v>
+      </c>
+      <c r="F5" s="7">
+        <f xml:space="preserve"> $C5 * Prices!$E4 + $D5 * Prices!$F4 + $E5 * Prices!$G4</f>
+        <v>1.029374201787995</v>
+      </c>
+      <c r="G5" s="9">
+        <f>(C4 * Prices!E3) / $F4</f>
+        <v>0.51596424010217112</v>
+      </c>
+      <c r="H5" s="9">
+        <f>(D4 * Prices!F3) / $F4</f>
+        <v>0.22988505747126436</v>
+      </c>
+      <c r="I5" s="9">
+        <f>(E4 * Prices!G3) / $F4</f>
+        <v>0.25415070242656451</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45661</v>
       </c>
@@ -1421,19 +1804,35 @@
         <v>45661</v>
       </c>
       <c r="C6" s="9">
-        <f>(C5 * Prices!D4) / $E5</f>
-        <v>0.50495049504950495</v>
+        <f>(C5 * Prices!E4) / $F5</f>
+        <v>0.50620347394540932</v>
       </c>
       <c r="D6" s="9">
-        <f>(D5 * Prices!E4) / E5</f>
-        <v>0.4950495049504951</v>
-      </c>
-      <c r="E6" s="7">
-        <f xml:space="preserve"> $C6 * Prices!$D5 + $D6 * Prices!$E5</f>
-        <v>0.95544554455445552</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D5 * Prices!F4) / $F5</f>
+        <v>0.24813895781637715</v>
+      </c>
+      <c r="E6" s="9">
+        <f>(E5 * Prices!G4) / $F5</f>
+        <v>0.24565756823821339</v>
+      </c>
+      <c r="F6" s="7">
+        <f xml:space="preserve"> $C6 * Prices!$E5 + $D6 * Prices!$F5 + $E6 * Prices!$G5</f>
+        <v>0.97890818858560769</v>
+      </c>
+      <c r="G6" s="9">
+        <f>(C5 * Prices!E4) / $F5</f>
+        <v>0.50620347394540932</v>
+      </c>
+      <c r="H6" s="9">
+        <f>(D5 * Prices!F4) / $F5</f>
+        <v>0.24813895781637715</v>
+      </c>
+      <c r="I6" s="9">
+        <f>(E5 * Prices!G4) / $F5</f>
+        <v>0.24565756823821339</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45662</v>
       </c>
@@ -1442,19 +1841,35 @@
         <v>45662</v>
       </c>
       <c r="C7" s="9">
-        <f>(C6 * Prices!D5) / $E6</f>
-        <v>0.53367875647668395</v>
+        <f>(C6 * Prices!E5) / $F6</f>
+        <v>0.52217997465145749</v>
       </c>
       <c r="D7" s="9">
-        <f>(D6 * Prices!E5) / E6</f>
-        <v>0.46632124352331611</v>
-      </c>
-      <c r="E7" s="7">
-        <f xml:space="preserve"> $C7 * Prices!$D6 + $D7 * Prices!$E6</f>
-        <v>1.0569948186528499</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D6 * Prices!F5) / $F6</f>
+        <v>0.22813688212927763</v>
+      </c>
+      <c r="E7" s="9">
+        <f>(E6 * Prices!G5) / $F6</f>
+        <v>0.24968314321926494</v>
+      </c>
+      <c r="F7" s="7">
+        <f xml:space="preserve"> $C7 * Prices!$E6 + $D7 * Prices!$F6 + $E7 * Prices!$G6</f>
+        <v>1.0291508238276299</v>
+      </c>
+      <c r="G7" s="9">
+        <f>(C6 * Prices!E5) / $F6</f>
+        <v>0.52217997465145749</v>
+      </c>
+      <c r="H7" s="9">
+        <f>(D6 * Prices!F5) / $F6</f>
+        <v>0.22813688212927763</v>
+      </c>
+      <c r="I7" s="9">
+        <f>(E6 * Prices!G5) / $F6</f>
+        <v>0.24968314321926494</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45663</v>
       </c>
@@ -1463,19 +1878,35 @@
         <v>45663</v>
       </c>
       <c r="C8" s="9">
-        <f>(C7 * Prices!D6) / $E7</f>
-        <v>0.50980392156862742</v>
+        <f>(C7 * Prices!E6) / $F7</f>
+        <v>0.51231527093596052</v>
       </c>
       <c r="D8" s="9">
-        <f>(D7 * Prices!E6) / E7</f>
-        <v>0.49019607843137253</v>
-      </c>
-      <c r="E8" s="7">
-        <f xml:space="preserve"> $C8 * Prices!$D7 + $D8 * Prices!$E7</f>
-        <v>0.95588235294117641</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D7 * Prices!F6) / $F7</f>
+        <v>0.24630541871921191</v>
+      </c>
+      <c r="E8" s="9">
+        <f>(E7 * Prices!G6) / $F7</f>
+        <v>0.24137931034482762</v>
+      </c>
+      <c r="F8" s="7">
+        <f xml:space="preserve"> $C8 * Prices!$E7 + $D8 * Prices!$F7 + $E8 * Prices!$G7</f>
+        <v>0.97906403940886699</v>
+      </c>
+      <c r="G8" s="9">
+        <f>(C7 * Prices!E6) / $F7</f>
+        <v>0.51231527093596052</v>
+      </c>
+      <c r="H8" s="9">
+        <f>(D7 * Prices!F6) / $F7</f>
+        <v>0.24630541871921191</v>
+      </c>
+      <c r="I8" s="9">
+        <f>(E7 * Prices!G6) / $F7</f>
+        <v>0.24137931034482762</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45664</v>
       </c>
@@ -1484,19 +1915,35 @@
         <v>45664</v>
       </c>
       <c r="C9" s="9">
-        <f>(C8 * Prices!D7) / $E8</f>
-        <v>0.53846153846153844</v>
+        <f>(C8 * Prices!E7) / $F8</f>
+        <v>0.52830188679245271</v>
       </c>
       <c r="D9" s="9">
-        <f>(D8 * Prices!E7) / E8</f>
-        <v>0.46153846153846156</v>
-      </c>
-      <c r="E9" s="7">
-        <f xml:space="preserve"> $C9 * Prices!$D8 + $D9 * Prices!$E8</f>
-        <v>1.0564102564102564</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D8 * Prices!F7) / $F8</f>
+        <v>0.22641509433962273</v>
+      </c>
+      <c r="E9" s="9">
+        <f>(E8 * Prices!G7) / $F8</f>
+        <v>0.24528301886792456</v>
+      </c>
+      <c r="F9" s="7">
+        <f xml:space="preserve"> $C9 * Prices!$E8 + $D9 * Prices!$F8 + $E9 * Prices!$G8</f>
+        <v>1.0289308176100629</v>
+      </c>
+      <c r="G9" s="9">
+        <f>(C8 * Prices!E7) / $F8</f>
+        <v>0.52830188679245271</v>
+      </c>
+      <c r="H9" s="9">
+        <f>(D8 * Prices!F7) / $F8</f>
+        <v>0.22641509433962273</v>
+      </c>
+      <c r="I9" s="9">
+        <f>(E8 * Prices!G7) / $F8</f>
+        <v>0.24528301886792456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45665</v>
       </c>
@@ -1505,19 +1952,35 @@
         <v>45665</v>
       </c>
       <c r="C10" s="9">
-        <f>(C9 * Prices!D8) / $E9</f>
-        <v>0.5145631067961165</v>
+        <f>(C9 * Prices!E8) / $F9</f>
+        <v>0.51833740831295827</v>
       </c>
       <c r="D10" s="9">
-        <f>(D9 * Prices!E8) / E9</f>
-        <v>0.48543689320388356</v>
-      </c>
-      <c r="E10" s="7">
-        <f xml:space="preserve"> $C10 * Prices!$D9 + $D10 * Prices!$E9</f>
-        <v>0.95631067961165073</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D9 * Prices!F8) / $F9</f>
+        <v>0.24449877750611257</v>
+      </c>
+      <c r="E10" s="9">
+        <f>(E9 * Prices!G8) / $F9</f>
+        <v>0.23716381418092913</v>
+      </c>
+      <c r="F10" s="7">
+        <f xml:space="preserve"> $C10 * Prices!$E9 + $D10 * Prices!$F9 + $E10 * Prices!$G9</f>
+        <v>0.97921760391198043</v>
+      </c>
+      <c r="G10" s="9">
+        <f>(C9 * Prices!E8) / $F9</f>
+        <v>0.51833740831295827</v>
+      </c>
+      <c r="H10" s="9">
+        <f>(D9 * Prices!F8) / $F9</f>
+        <v>0.24449877750611257</v>
+      </c>
+      <c r="I10" s="9">
+        <f>(E9 * Prices!G8) / $F9</f>
+        <v>0.23716381418092913</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45666</v>
       </c>
@@ -1526,19 +1989,35 @@
         <v>45666</v>
       </c>
       <c r="C11" s="9">
-        <f>(C10 * Prices!D9) / $E10</f>
-        <v>0.54314720812182737</v>
+        <f>(C10 * Prices!E9) / $F10</f>
+        <v>0.53433208489388251</v>
       </c>
       <c r="D11" s="9">
-        <f>(D10 * Prices!E9) / E10</f>
-        <v>0.45685279187817257</v>
-      </c>
-      <c r="E11" s="7">
-        <f xml:space="preserve"> $C11 * Prices!$D10 + $D11 * Prices!$E10</f>
-        <v>1.0558375634517765</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D10 * Prices!F9) / $F10</f>
+        <v>0.22471910112359561</v>
+      </c>
+      <c r="E11" s="9">
+        <f>(E10 * Prices!G9) / $F10</f>
+        <v>0.24094881398252188</v>
+      </c>
+      <c r="F11" s="7">
+        <f xml:space="preserve"> $C11 * Prices!$E10 + $D11 * Prices!$F10 + $E11 * Prices!$G10</f>
+        <v>1.0287141073657926</v>
+      </c>
+      <c r="G11" s="9">
+        <f>(C10 * Prices!E9) / $F10</f>
+        <v>0.53433208489388251</v>
+      </c>
+      <c r="H11" s="9">
+        <f>(D10 * Prices!F9) / $F10</f>
+        <v>0.22471910112359561</v>
+      </c>
+      <c r="I11" s="9">
+        <f>(E10 * Prices!G9) / $F10</f>
+        <v>0.24094881398252188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45667</v>
       </c>
@@ -1547,19 +2026,35 @@
         <v>45667</v>
       </c>
       <c r="C12" s="9">
-        <f>(C11 * Prices!D10) / $E11</f>
-        <v>0.51923076923076916</v>
+        <f>(C11 * Prices!E10) / $F11</f>
+        <v>0.52427184466019405</v>
       </c>
       <c r="D12" s="9">
-        <f>(D11 * Prices!E10) / E11</f>
-        <v>0.48076923076923084</v>
-      </c>
-      <c r="E12" s="7">
-        <f xml:space="preserve"> $C12 * Prices!$D11 + $D12 * Prices!$E11</f>
-        <v>0.95673076923076916</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D11 * Prices!F10) / $F11</f>
+        <v>0.24271844660194192</v>
+      </c>
+      <c r="E12" s="9">
+        <f>(E11 * Prices!G10) / $F11</f>
+        <v>0.23300970873786414</v>
+      </c>
+      <c r="F12" s="7">
+        <f xml:space="preserve"> $C12 * Prices!$E11 + $D12 * Prices!$F11 + $E12 * Prices!$G11</f>
+        <v>0.97936893203883502</v>
+      </c>
+      <c r="G12" s="9">
+        <f>(C11 * Prices!E10) / $F11</f>
+        <v>0.52427184466019405</v>
+      </c>
+      <c r="H12" s="9">
+        <f>(D11 * Prices!F10) / $F11</f>
+        <v>0.24271844660194192</v>
+      </c>
+      <c r="I12" s="9">
+        <f>(E11 * Prices!G10) / $F11</f>
+        <v>0.23300970873786414</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45668</v>
       </c>
@@ -1568,19 +2063,35 @@
         <v>45668</v>
       </c>
       <c r="C13" s="9">
-        <f>(C12 * Prices!D11) / $E12</f>
-        <v>0.54773869346733661</v>
+        <f>(C12 * Prices!E11) / $F12</f>
+        <v>0.54027261462205689</v>
       </c>
       <c r="D13" s="9">
-        <f>(D12 * Prices!E11) / E12</f>
-        <v>0.45226130653266344</v>
-      </c>
-      <c r="E13" s="7">
-        <f xml:space="preserve"> $C13 * Prices!$D12 + $D13 * Prices!$E12</f>
-        <v>1.0552763819095479</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D12 * Prices!F11) / $F12</f>
+        <v>0.2230483271375466</v>
+      </c>
+      <c r="E13" s="9">
+        <f>(E12 * Prices!G11) / $F12</f>
+        <v>0.23667905824039659</v>
+      </c>
+      <c r="F13" s="7">
+        <f xml:space="preserve"> $C13 * Prices!$E12 + $D13 * Prices!$F12 + $E13 * Prices!$G12</f>
+        <v>1.0285006195786865</v>
+      </c>
+      <c r="G13" s="9">
+        <f>(C12 * Prices!E11) / $F12</f>
+        <v>0.54027261462205689</v>
+      </c>
+      <c r="H13" s="9">
+        <f>(D12 * Prices!F11) / $F12</f>
+        <v>0.2230483271375466</v>
+      </c>
+      <c r="I13" s="9">
+        <f>(E12 * Prices!G11) / $F12</f>
+        <v>0.23667905824039659</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45669</v>
       </c>
@@ -1589,19 +2100,35 @@
         <v>45669</v>
       </c>
       <c r="C14" s="9">
-        <f>(C13 * Prices!D12) / $E13</f>
-        <v>0.52380952380952372</v>
+        <f>(C13 * Prices!E12) / $F13</f>
+        <v>0.53012048192771066</v>
       </c>
       <c r="D14" s="9">
-        <f>(D13 * Prices!E12) / E13</f>
-        <v>0.47619047619047628</v>
-      </c>
-      <c r="E14" s="7">
-        <f xml:space="preserve"> $C14 * Prices!$D13 + $D14 * Prices!$E13</f>
-        <v>0.95714285714285707</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D13 * Prices!F12) / $F13</f>
+        <v>0.24096385542168688</v>
+      </c>
+      <c r="E14" s="9">
+        <f>(E13 * Prices!G12) / $F13</f>
+        <v>0.22891566265060248</v>
+      </c>
+      <c r="F14" s="7">
+        <f xml:space="preserve"> $C14 * Prices!$E13 + $D14 * Prices!$F13 + $E14 * Prices!$G13</f>
+        <v>0.97951807228915655</v>
+      </c>
+      <c r="G14" s="9">
+        <f>(C13 * Prices!E12) / $F13</f>
+        <v>0.53012048192771066</v>
+      </c>
+      <c r="H14" s="9">
+        <f>(D13 * Prices!F12) / $F13</f>
+        <v>0.24096385542168688</v>
+      </c>
+      <c r="I14" s="9">
+        <f>(E13 * Prices!G12) / $F13</f>
+        <v>0.22891566265060248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45670</v>
       </c>
@@ -1609,19 +2136,35 @@
         <f t="shared" si="0"/>
         <v>45670</v>
       </c>
-      <c r="C15" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="E15" s="7">
-        <f xml:space="preserve"> $C15 * Prices!$D14 + $D15 * Prices!$E14</f>
-        <v>1.0575075075075075</v>
-      </c>
-      <c r="G15" s="9"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C15" s="15">
+        <f>1-D15-E15</f>
+        <v>0.53002767527675265</v>
+      </c>
+      <c r="D15" s="14">
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="E15" s="8">
+        <f>(E14 * Prices!G13) / $F14</f>
+        <v>0.2324723247232473</v>
+      </c>
+      <c r="F15" s="7">
+        <f xml:space="preserve"> $C15 * Prices!$E14 + $D15 * Prices!$F14 + $E15 * Prices!$G14</f>
+        <v>1.0299339006903581</v>
+      </c>
+      <c r="G15" s="14">
+        <f>(C14 * Prices!E13) / $F14</f>
+        <v>0.54612546125461237</v>
+      </c>
+      <c r="H15" s="8">
+        <f>(D14 * Prices!F13) / $F14</f>
+        <v>0.22140221402214036</v>
+      </c>
+      <c r="I15" s="9">
+        <f>(E14 * Prices!G13) / $F14</f>
+        <v>0.2324723247232473</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45671</v>
       </c>
@@ -1630,19 +2173,35 @@
         <v>45671</v>
       </c>
       <c r="C16" s="9">
-        <f>(C15 * Prices!D14) / $E15</f>
-        <v>0.50092290217236979</v>
+        <f>(C15 * Prices!E14) / $F15</f>
+        <v>0.51925924471451057</v>
       </c>
       <c r="D16" s="9">
-        <f>(D15 * Prices!E14) / E15</f>
-        <v>0.49907709782763027</v>
-      </c>
-      <c r="E16" s="7">
-        <f xml:space="preserve"> $C16 * Prices!$D15 + $D16 * Prices!$E15</f>
-        <v>0.9545648161294904</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D15 * Prices!F14) / $F15</f>
+        <v>0.25621924738277463</v>
+      </c>
+      <c r="E16" s="9">
+        <f>(E15 * Prices!G14) / $F15</f>
+        <v>0.22452150790271497</v>
+      </c>
+      <c r="F16" s="7">
+        <f xml:space="preserve"> $C16 * Prices!$E15 + $D16 * Prices!$F15 + $E16 * Prices!$G15</f>
+        <v>0.97782005517819415</v>
+      </c>
+      <c r="G16" s="9">
+        <f>(C15 * Prices!E14) / $F15</f>
+        <v>0.51925924471451057</v>
+      </c>
+      <c r="H16" s="9">
+        <f>(D15 * Prices!F14) / $F15</f>
+        <v>0.25621924738277463</v>
+      </c>
+      <c r="I16" s="9">
+        <f>(E15 * Prices!G14) / $F15</f>
+        <v>0.22452150790271497</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45672</v>
       </c>
@@ -1651,19 +2210,35 @@
         <v>45672</v>
       </c>
       <c r="C17" s="9">
-        <f>(C16 * Prices!D15) / $E16</f>
-        <v>0.52945113788487286</v>
+        <f>(C16 * Prices!E15) / $F16</f>
+        <v>0.53577903745839761</v>
       </c>
       <c r="D17" s="9">
-        <f>(D16 * Prices!E15) / E16</f>
-        <v>0.47054886211512709</v>
-      </c>
-      <c r="E17" s="7">
-        <f xml:space="preserve"> $C17 * Prices!$D16 + $D17 * Prices!$E16</f>
-        <v>1.0569686152015469</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D16 * Prices!F15) / $F16</f>
+        <v>0.23582797409741613</v>
+      </c>
+      <c r="E17" s="9">
+        <f>(E16 * Prices!G15) / $F16</f>
+        <v>0.22839298844418629</v>
+      </c>
+      <c r="F17" s="7">
+        <f xml:space="preserve"> $C17 * Prices!$E16 + $D17 * Prices!$F16 + $E17 * Prices!$G16</f>
+        <v>1.0297231627648018</v>
+      </c>
+      <c r="G17" s="9">
+        <f>(C16 * Prices!E15) / $F16</f>
+        <v>0.53577903745839761</v>
+      </c>
+      <c r="H17" s="9">
+        <f>(D16 * Prices!F15) / $F16</f>
+        <v>0.23582797409741613</v>
+      </c>
+      <c r="I17" s="9">
+        <f>(E16 * Prices!G15) / $F16</f>
+        <v>0.22839298844418629</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45673</v>
       </c>
@@ -1672,19 +2247,35 @@
         <v>45673</v>
       </c>
       <c r="C18" s="9">
-        <f>(C17 * Prices!D16) / $E17</f>
-        <v>0.50534759358288783</v>
+        <f>(C17 * Prices!E16) / $F17</f>
+        <v>0.5249182153174442</v>
       </c>
       <c r="D18" s="9">
-        <f>(D17 * Prices!E16) / E17</f>
-        <v>0.49465240641711222</v>
-      </c>
-      <c r="E18" s="7">
-        <f xml:space="preserve"> $C18 * Prices!$D17 + $D18 * Prices!$E17</f>
-        <v>0.9549676329862089</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D17 * Prices!F16) / $F17</f>
+        <v>0.25446750331119106</v>
+      </c>
+      <c r="E18" s="9">
+        <f>(E17 * Prices!G16) / $F17</f>
+        <v>0.22061428137136474</v>
+      </c>
+      <c r="F18" s="7">
+        <f xml:space="preserve"> $C18 * Prices!$E17 + $D18 * Prices!$F17 + $E18 * Prices!$G17</f>
+        <v>0.97797169713033671</v>
+      </c>
+      <c r="G18" s="9">
+        <f>(C17 * Prices!E16) / $F17</f>
+        <v>0.5249182153174442</v>
+      </c>
+      <c r="H18" s="9">
+        <f>(D17 * Prices!F16) / $F17</f>
+        <v>0.25446750331119106</v>
+      </c>
+      <c r="I18" s="9">
+        <f>(E17 * Prices!G16) / $F17</f>
+        <v>0.22061428137136474</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45674</v>
       </c>
@@ -1693,19 +2284,35 @@
         <v>45674</v>
       </c>
       <c r="C19" s="9">
-        <f>(C18 * Prices!D17) / $E18</f>
-        <v>0.53381962864721499</v>
+        <f>(C18 * Prices!E17) / $F18</f>
+        <v>0.54144998533149991</v>
       </c>
       <c r="D19" s="9">
-        <f>(D18 * Prices!E17) / E18</f>
-        <v>0.46618037135278506</v>
-      </c>
-      <c r="E19" s="7">
-        <f xml:space="preserve"> $C19 * Prices!$D18 + $D19 * Prices!$E18</f>
-        <v>1.0564397288535221</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D18 * Prices!F17) / $F18</f>
+        <v>0.23417932610124381</v>
+      </c>
+      <c r="E19" s="9">
+        <f>(E18 * Prices!G17) / $F18</f>
+        <v>0.22437068856725634</v>
+      </c>
+      <c r="F19" s="7">
+        <f xml:space="preserve"> $C19 * Prices!$E18 + $D19 * Prices!$F18 + $E19 * Prices!$G18</f>
+        <v>1.0295153713315777</v>
+      </c>
+      <c r="G19" s="9">
+        <f>(C18 * Prices!E17) / $F18</f>
+        <v>0.54144998533149991</v>
+      </c>
+      <c r="H19" s="9">
+        <f>(D18 * Prices!F17) / $F18</f>
+        <v>0.23417932610124381</v>
+      </c>
+      <c r="I19" s="9">
+        <f>(E18 * Prices!G17) / $F18</f>
+        <v>0.22437068856725634</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45675</v>
       </c>
@@ -1714,19 +2321,35 @@
         <v>45675</v>
       </c>
       <c r="C20" s="9">
-        <f>(C19 * Prices!D18) / $E19</f>
-        <v>0.50969451806388621</v>
+        <f>(C19 * Prices!E18) / $F19</f>
+        <v>0.53050033178922873</v>
       </c>
       <c r="D20" s="9">
-        <f>(D19 * Prices!E18) / E19</f>
-        <v>0.49030548193611373</v>
-      </c>
-      <c r="E20" s="7">
-        <f xml:space="preserve"> $C20 * Prices!$D19 + $D20 * Prices!$E19</f>
-        <v>0.95536337006556005</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D19 * Prices!F18) / $F19</f>
+        <v>0.2527395495679311</v>
+      </c>
+      <c r="E20" s="9">
+        <f>(E19 * Prices!G18) / $F19</f>
+        <v>0.21676011864284009</v>
+      </c>
+      <c r="F20" s="7">
+        <f xml:space="preserve"> $C20 * Prices!$E19 + $D20 * Prices!$F19 + $E20 * Prices!$G19</f>
+        <v>0.97812127964246887</v>
+      </c>
+      <c r="G20" s="9">
+        <f>(C19 * Prices!E18) / $F19</f>
+        <v>0.53050033178922873</v>
+      </c>
+      <c r="H20" s="9">
+        <f>(D19 * Prices!F18) / $F19</f>
+        <v>0.2527395495679311</v>
+      </c>
+      <c r="I20" s="9">
+        <f>(E19 * Prices!G18) / $F19</f>
+        <v>0.21676011864284009</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45676</v>
       </c>
@@ -1735,19 +2358,35 @@
         <v>45676</v>
       </c>
       <c r="C21" s="9">
-        <f>(C20 * Prices!D19) / $E20</f>
-        <v>0.53810775295663604</v>
+        <f>(C20 * Prices!E19) / $F20</f>
+        <v>0.54704219369108731</v>
       </c>
       <c r="D21" s="9">
-        <f>(D20 * Prices!E19) / E20</f>
-        <v>0.4618922470433639</v>
-      </c>
-      <c r="E21" s="7">
-        <f xml:space="preserve"> $C21 * Prices!$D20 + $D21 * Prices!$E20</f>
-        <v>1.0559205723463279</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D20 * Prices!F19) / $F20</f>
+        <v>0.23255356911801686</v>
+      </c>
+      <c r="E21" s="9">
+        <f>(E20 * Prices!G19) / $F20</f>
+        <v>0.22040423719089575</v>
+      </c>
+      <c r="F21" s="7">
+        <f xml:space="preserve"> $C21 * Prices!$E20 + $D21 * Prices!$F20 + $E21 * Prices!$G20</f>
+        <v>1.0293104650238614</v>
+      </c>
+      <c r="G21" s="9">
+        <f>(C20 * Prices!E19) / $F20</f>
+        <v>0.54704219369108731</v>
+      </c>
+      <c r="H21" s="9">
+        <f>(D20 * Prices!F19) / $F20</f>
+        <v>0.23255356911801686</v>
+      </c>
+      <c r="I21" s="9">
+        <f>(E20 * Prices!G19) / $F20</f>
+        <v>0.22040423719089575</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45677</v>
       </c>
@@ -1755,20 +2394,35 @@
         <f t="shared" si="0"/>
         <v>45677</v>
       </c>
-      <c r="C22" s="9">
-        <f>(C21 * Prices!D20) / $E21</f>
-        <v>0.51396570796460184</v>
+      <c r="C22" s="15">
+        <f>1-D22-E22</f>
+        <v>0.51146509522072692</v>
       </c>
       <c r="D22" s="9">
-        <f>(D21 * Prices!E20) / E21</f>
-        <v>0.48603429203539822</v>
-      </c>
-      <c r="E22" s="7">
-        <f xml:space="preserve"> $C22 * Prices!$D21 + $D22 * Prices!$E21</f>
-        <v>0.95575221238938057</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D21 * Prices!F20) / $F21</f>
+        <v>0.25103490477927304</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="F22" s="7">
+        <f xml:space="preserve"> $C22 * Prices!$E21 + $D22 * Prices!$F21 + $E22 * Prices!$G21</f>
+        <v>0.9779260144266253</v>
+      </c>
+      <c r="G22" s="9">
+        <f>(C21 * Prices!E20) / $F21</f>
+        <v>0.53600714919705927</v>
+      </c>
+      <c r="H22" s="9">
+        <f>(D21 * Prices!F20) / $F21</f>
+        <v>0.25103490477927304</v>
+      </c>
+      <c r="I22" s="8">
+        <f>(E21 * Prices!G20) / $F21</f>
+        <v>0.21295794602366763</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45678</v>
       </c>
@@ -1777,19 +2431,35 @@
         <v>45678</v>
       </c>
       <c r="C23" s="9">
-        <f>(C22 * Prices!D21) / $E22</f>
-        <v>0.54231770833333337</v>
+        <f>(C22 * Prices!E21) / $F22</f>
+        <v>0.52744229887641014</v>
       </c>
       <c r="D23" s="9">
-        <f>(D22 * Prices!E21) / E22</f>
-        <v>0.45768229166666663</v>
-      </c>
-      <c r="E23" s="7">
-        <f xml:space="preserve"> $C23 * Prices!$D22 + $D23 * Prices!$E22</f>
-        <v>1.0554108796296298</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D22 * Prices!F21) / $F22</f>
+        <v>0.23103119353442417</v>
+      </c>
+      <c r="E23" s="9">
+        <f>(E22 * Prices!G21) / $F22</f>
+        <v>0.24152650758916575</v>
+      </c>
+      <c r="F23" s="7">
+        <f xml:space="preserve"> $C23 * Prices!$E22 + $D23 * Prices!$F22 + $E23 * Prices!$G22</f>
+        <v>1.0287680202463729</v>
+      </c>
+      <c r="G23" s="9">
+        <f>(C22 * Prices!E21) / $F22</f>
+        <v>0.52744229887641014</v>
+      </c>
+      <c r="H23" s="9">
+        <f>(D22 * Prices!F21) / $F22</f>
+        <v>0.23103119353442417</v>
+      </c>
+      <c r="I23" s="9">
+        <f>(E22 * Prices!G21) / $F22</f>
+        <v>0.24152650758916575</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45679</v>
       </c>
@@ -1798,19 +2468,35 @@
         <v>45679</v>
       </c>
       <c r="C24" s="9">
-        <f>(C23 * Prices!D22) / $E23</f>
-        <v>0.5181631254283755</v>
+        <f>(C23 * Prices!E22) / $F23</f>
+        <v>0.51700147811251673</v>
       </c>
       <c r="D24" s="9">
-        <f>(D23 * Prices!E22) / E23</f>
-        <v>0.48183687457162439</v>
-      </c>
-      <c r="E24" s="7">
-        <f xml:space="preserve"> $C24 * Prices!$D23 + $D24 * Prices!$E23</f>
-        <v>0.95613433858807384</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D23 * Prices!F22) / $F23</f>
+        <v>0.24952304221887114</v>
+      </c>
+      <c r="E24" s="9">
+        <f>(E23 * Prices!G22) / $F23</f>
+        <v>0.23347547966861221</v>
+      </c>
+      <c r="F24" s="7">
+        <f xml:space="preserve"> $C24 * Prices!$E23 + $D24 * Prices!$F23 + $E24 * Prices!$G23</f>
+        <v>0.97805895543089161</v>
+      </c>
+      <c r="G24" s="9">
+        <f>(C23 * Prices!E22) / $F23</f>
+        <v>0.51700147811251673</v>
+      </c>
+      <c r="H24" s="9">
+        <f>(D23 * Prices!F22) / $F23</f>
+        <v>0.24952304221887114</v>
+      </c>
+      <c r="I24" s="9">
+        <f>(E23 * Prices!G22) / $F23</f>
+        <v>0.23347547966861221</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45680</v>
       </c>
@@ -1819,19 +2505,35 @@
         <v>45680</v>
       </c>
       <c r="C25" s="9">
-        <f>(C24 * Prices!D23) / $E24</f>
-        <v>0.54645161290322586</v>
+        <f>(C24 * Prices!E23) / $F24</f>
+        <v>0.53300449923674309</v>
       </c>
       <c r="D25" s="9">
-        <f>(D24 * Prices!E23) / E24</f>
-        <v>0.45354838709677425</v>
-      </c>
-      <c r="E25" s="7">
-        <f xml:space="preserve"> $C25 * Prices!$D24 + $D25 * Prices!$E24</f>
-        <v>1.0549103942652331</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D24 * Prices!F23) / $F24</f>
+        <v>0.22960859031043546</v>
+      </c>
+      <c r="E25" s="9">
+        <f>(E24 * Prices!G23) / $F24</f>
+        <v>0.23738691045282156</v>
+      </c>
+      <c r="F25" s="7">
+        <f xml:space="preserve"> $C25 * Prices!$E24 + $D25 * Prices!$F24 + $E25 * Prices!$G24</f>
+        <v>1.028590877594231</v>
+      </c>
+      <c r="G25" s="9">
+        <f>(C24 * Prices!E23) / $F24</f>
+        <v>0.53300449923674309</v>
+      </c>
+      <c r="H25" s="9">
+        <f>(D24 * Prices!F23) / $F24</f>
+        <v>0.22960859031043546</v>
+      </c>
+      <c r="I25" s="9">
+        <f>(E24 * Prices!G23) / $F24</f>
+        <v>0.23738691045282156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45681</v>
       </c>
@@ -1840,19 +2542,35 @@
         <v>45681</v>
       </c>
       <c r="C26" s="9">
-        <f>(C25 * Prices!D24) / $E25</f>
-        <v>0.52228866539820595</v>
+        <f>(C25 * Prices!E24) / $F25</f>
+        <v>0.52247157427173541</v>
       </c>
       <c r="D26" s="9">
-        <f>(D25 * Prices!E24) / E25</f>
-        <v>0.47771133460179399</v>
-      </c>
-      <c r="E26" s="7">
-        <f xml:space="preserve"> $C26 * Prices!$D25 + $D26 * Prices!$E25</f>
-        <v>0.95650992117423195</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D25 * Prices!F24) / $F25</f>
+        <v>0.24802928108519201</v>
+      </c>
+      <c r="E26" s="9">
+        <f>(E25 * Prices!G24) / $F25</f>
+        <v>0.22949914464307244</v>
+      </c>
+      <c r="F26" s="7">
+        <f xml:space="preserve"> $C26 * Prices!$E25 + $D26 * Prices!$F25 + $E26 * Prices!$G25</f>
+        <v>0.97819030474163327</v>
+      </c>
+      <c r="G26" s="9">
+        <f>(C25 * Prices!E24) / $F25</f>
+        <v>0.52247157427173541</v>
+      </c>
+      <c r="H26" s="9">
+        <f>(D25 * Prices!F24) / $F25</f>
+        <v>0.24802928108519201</v>
+      </c>
+      <c r="I26" s="9">
+        <f>(E25 * Prices!G24) / $F25</f>
+        <v>0.22949914464307244</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45682</v>
       </c>
@@ -1861,19 +2579,35 @@
         <v>45682</v>
       </c>
       <c r="C27" s="9">
-        <f>(C26 * Prices!D25) / $E26</f>
-        <v>0.55051150895140655</v>
+        <f>(C26 * Prices!E25) / $F26</f>
+        <v>0.53849861893523754</v>
       </c>
       <c r="D27" s="9">
-        <f>(D26 * Prices!E25) / E26</f>
-        <v>0.44948849104859345</v>
-      </c>
-      <c r="E27" s="7">
-        <f xml:space="preserve"> $C27 * Prices!$D26 + $D27 * Prices!$E26</f>
-        <v>1.0544188689968741</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D26 * Prices!F25) / $F26</f>
+        <v>0.22820339957840105</v>
+      </c>
+      <c r="E27" s="9">
+        <f>(E26 * Prices!G25) / $F26</f>
+        <v>0.23329798148636144</v>
+      </c>
+      <c r="F27" s="7">
+        <f xml:space="preserve"> $C27 * Prices!$E26 + $D27 * Prices!$F26 + $E27 * Prices!$G26</f>
+        <v>1.0284159031467945</v>
+      </c>
+      <c r="G27" s="9">
+        <f>(C26 * Prices!E25) / $F26</f>
+        <v>0.53849861893523754</v>
+      </c>
+      <c r="H27" s="9">
+        <f>(D26 * Prices!F25) / $F26</f>
+        <v>0.22820339957840105</v>
+      </c>
+      <c r="I27" s="9">
+        <f>(E26 * Prices!G25) / $F26</f>
+        <v>0.23329798148636144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45683</v>
       </c>
@@ -1882,19 +2616,35 @@
         <v>45683</v>
       </c>
       <c r="C28" s="9">
-        <f>(C27 * Prices!D26) / $E27</f>
-        <v>0.5263441584692089</v>
+        <f>(C27 * Prices!E26) / $F27</f>
+        <v>0.52787656708383968</v>
       </c>
       <c r="D28" s="9">
-        <f>(D27 * Prices!E26) / E27</f>
-        <v>0.47365584153079116</v>
-      </c>
-      <c r="E28" s="7">
-        <f xml:space="preserve"> $C28 * Prices!$D27 + $D28 * Prices!$E27</f>
-        <v>0.95687912680231779</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D27 * Prices!F26) / $F27</f>
+        <v>0.24655329822208846</v>
+      </c>
+      <c r="E28" s="9">
+        <f>(E27 * Prices!G26) / $F27</f>
+        <v>0.22557013469407194</v>
+      </c>
+      <c r="F28" s="7">
+        <f xml:space="preserve"> $C28 * Prices!$E27 + $D28 * Prices!$F27 + $E28 * Prices!$G27</f>
+        <v>0.97832009077459714</v>
+      </c>
+      <c r="G28" s="9">
+        <f>(C27 * Prices!E26) / $F27</f>
+        <v>0.52787656708383968</v>
+      </c>
+      <c r="H28" s="9">
+        <f>(D27 * Prices!F26) / $F27</f>
+        <v>0.24655329822208846</v>
+      </c>
+      <c r="I28" s="9">
+        <f>(E27 * Prices!G26) / $F27</f>
+        <v>0.22557013469407194</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45684</v>
       </c>
@@ -1902,19 +2652,36 @@
         <f t="shared" si="0"/>
         <v>45684</v>
       </c>
-      <c r="C29" s="8">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="D29" s="8">
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="E29" s="7">
-        <f xml:space="preserve"> $C29 * Prices!$D28 + $D29 * Prices!$E28</f>
-        <v>1.0569777777777778</v>
-      </c>
-      <c r="G29" s="9"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C29" s="9">
+        <f>(C28 * Prices!E27) / $F28</f>
+        <v>0.54392590031745347</v>
+      </c>
+      <c r="D29" s="9">
+        <f>(D28 * Prices!F27) / $F28</f>
+        <v>0.22681530359270161</v>
+      </c>
+      <c r="E29" s="9">
+        <f>(E28 * Prices!G27) / $F28</f>
+        <v>0.22925879608984495</v>
+      </c>
+      <c r="F29" s="7">
+        <f xml:space="preserve"> $C29 * Prices!$E28 + $D29 * Prices!$F28 + $E29 * Prices!$G28</f>
+        <v>1.0282430573383583</v>
+      </c>
+      <c r="G29" s="9">
+        <f>(C28 * Prices!E27) / $F28</f>
+        <v>0.54392590031745347</v>
+      </c>
+      <c r="H29" s="9">
+        <f>(D28 * Prices!F27) / $F28</f>
+        <v>0.22681530359270161</v>
+      </c>
+      <c r="I29" s="9">
+        <f>(E28 * Prices!G27) / $F28</f>
+        <v>0.22925879608984495</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45685</v>
       </c>
@@ -1923,19 +2690,35 @@
         <v>45685</v>
       </c>
       <c r="C30" s="9">
-        <f>(C29 * Prices!D28) / $E29</f>
-        <v>0.50067277773105712</v>
+        <f>(C29 * Prices!E28) / $F29</f>
+        <v>0.53321761193236483</v>
       </c>
       <c r="D30" s="9">
-        <f>(D29 * Prices!E28) / E29</f>
-        <v>0.49932722226894288</v>
-      </c>
-      <c r="E30" s="7">
-        <f xml:space="preserve"> $C30 * Prices!$D29 + $D30 * Prices!$E29</f>
-        <v>0.95404087124716175</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D29 * Prices!F28) / $F29</f>
+        <v>0.24509477812011216</v>
+      </c>
+      <c r="E30" s="9">
+        <f>(E29 * Prices!G28) / $F29</f>
+        <v>0.22168760994752293</v>
+      </c>
+      <c r="F30" s="7">
+        <f xml:space="preserve"> $C30 * Prices!$E29 + $D30 * Prices!$F29 + $E30 * Prices!$G29</f>
+        <v>0.9784483412731394</v>
+      </c>
+      <c r="G30" s="9">
+        <f>(C29 * Prices!E28) / $F29</f>
+        <v>0.53321761193236483</v>
+      </c>
+      <c r="H30" s="9">
+        <f>(D29 * Prices!F28) / $F29</f>
+        <v>0.24509477812011216</v>
+      </c>
+      <c r="I30" s="9">
+        <f>(E29 * Prices!G28) / $F29</f>
+        <v>0.22168760994752293</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45686</v>
       </c>
@@ -1944,19 +2727,35 @@
         <v>45686</v>
       </c>
       <c r="C31" s="9">
-        <f>(C30 * Prices!D29) / $E30</f>
-        <v>0.52895676318921059</v>
+        <f>(C30 * Prices!E29) / $F30</f>
+        <v>0.54928755568437293</v>
       </c>
       <c r="D31" s="9">
-        <f>(D30 * Prices!E29) / E30</f>
-        <v>0.47104323681078936</v>
-      </c>
-      <c r="E31" s="7">
-        <f xml:space="preserve"> $C31 * Prices!$D30 + $D31 * Prices!$E30</f>
-        <v>1.0565031513068006</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+        <f>(D30 * Prices!F29) / $F30</f>
+        <v>0.2254439922919991</v>
+      </c>
+      <c r="E31" s="9">
+        <f>(E30 * Prices!G29) / $F30</f>
+        <v>0.225268452023628</v>
+      </c>
+      <c r="F31" s="7">
+        <f xml:space="preserve"> $C31 * Prices!$E30 + $D31 * Prices!$F30 + $E31 * Prices!$G30</f>
+        <v>1.0280723015600619</v>
+      </c>
+      <c r="G31" s="9">
+        <f>(C30 * Prices!E29) / $F30</f>
+        <v>0.54928755568437293</v>
+      </c>
+      <c r="H31" s="9">
+        <f>(D30 * Prices!F29) / $F30</f>
+        <v>0.2254439922919991</v>
+      </c>
+      <c r="I31" s="9">
+        <f>(E30 * Prices!G29) / $F30</f>
+        <v>0.225268452023628</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45687</v>
       </c>
@@ -1965,19 +2764,35 @@
         <v>45687</v>
       </c>
       <c r="C32" s="9">
-        <f>(C31 * Prices!D30) / $E31</f>
-        <v>0.504609736765258</v>
+        <f>(C31 * Prices!E30) / $F31</f>
+        <v>0.53849583702230142</v>
       </c>
       <c r="D32" s="9">
-        <f>(D31 * Prices!E30) / E31</f>
-        <v>0.49539026323474195</v>
-      </c>
-      <c r="E32" s="7">
-        <f xml:space="preserve"> $C32 * Prices!$D31 + $D32 * Prices!$E31</f>
-        <v>0.95440323724500442</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+        <f>(D31 * Prices!F30) / $F31</f>
+        <v>0.24365341269166915</v>
+      </c>
+      <c r="E32" s="9">
+        <f>(E31 * Prices!G30) / $F31</f>
+        <v>0.21785075028602943</v>
+      </c>
+      <c r="F32" s="7">
+        <f xml:space="preserve"> $C32 * Prices!$E31 + $D32 * Prices!$F31 + $E32 * Prices!$G31</f>
+        <v>0.97857508332799981</v>
+      </c>
+      <c r="G32" s="9">
+        <f>(C31 * Prices!E30) / $F31</f>
+        <v>0.53849583702230142</v>
+      </c>
+      <c r="H32" s="9">
+        <f>(D31 * Prices!F30) / $F31</f>
+        <v>0.24365341269166915</v>
+      </c>
+      <c r="I32" s="9">
+        <f>(E31 * Prices!G30) / $F31</f>
+        <v>0.21785075028602943</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45688</v>
       </c>
@@ -1986,19 +2801,35 @@
         <v>45688</v>
       </c>
       <c r="C33" s="9">
-        <f>(C32 * Prices!D31) / $E32</f>
-        <v>0.53284815106215577</v>
+        <f>(C32 * Prices!E31) / $F32</f>
+        <v>0.55458476819518043</v>
       </c>
       <c r="D33" s="9">
-        <f>(D32 * Prices!E31) / E32</f>
-        <v>0.46715184893784417</v>
-      </c>
-      <c r="E33" s="7">
-        <f xml:space="preserve"> $C33 * Prices!$D32 + $D33 * Prices!$E32</f>
-        <v>1.056036366815281</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+        <f>(D32 * Prices!F31) / $F32</f>
+        <v>0.22408916306833968</v>
+      </c>
+      <c r="E33" s="9">
+        <f>(E32 * Prices!G31) / $F32</f>
+        <v>0.22132606873647998</v>
+      </c>
+      <c r="F33" s="7">
+        <f xml:space="preserve"> $C33 * Prices!$E32 + $D33 * Prices!$F32 + $E33 * Prices!$G32</f>
+        <v>1.0279035981311424</v>
+      </c>
+      <c r="G33" s="9">
+        <f>(C32 * Prices!E31) / $F32</f>
+        <v>0.55458476819518043</v>
+      </c>
+      <c r="H33" s="9">
+        <f>(D32 * Prices!F31) / $F32</f>
+        <v>0.22408916306833968</v>
+      </c>
+      <c r="I33" s="9">
+        <f>(E32 * Prices!G31) / $F32</f>
+        <v>0.22132606873647998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>45689</v>
       </c>
@@ -2007,16 +2838,32 @@
         <v>45689</v>
       </c>
       <c r="C34" s="9">
-        <f>(C33 * Prices!D32) / $E33</f>
-        <v>0.50848509933774833</v>
+        <f>(C33 * Prices!E32) / $F33</f>
+        <v>0.54371234417458658</v>
       </c>
       <c r="D34" s="9">
-        <f>(D33 * Prices!E32) / E33</f>
-        <v>0.49151490066225162</v>
-      </c>
-      <c r="E34" s="7">
-        <f xml:space="preserve"> $C34 * Prices!$D33 + $D34 * Prices!$E33</f>
-        <v>0.95475993377483437</v>
+        <f>(D33 * Prices!F32) / $F33</f>
+        <v>0.24222890105406109</v>
+      </c>
+      <c r="E34" s="9">
+        <f>(E33 * Prices!G32) / $F33</f>
+        <v>0.21405875477135242</v>
+      </c>
+      <c r="F34" s="7">
+        <f xml:space="preserve"> $C34 * Prices!$E33 + $D34 * Prices!$F33 + $E34 * Prices!$G33</f>
+        <v>0.97870034339637701</v>
+      </c>
+      <c r="G34" s="9">
+        <f>(C33 * Prices!E32) / $F33</f>
+        <v>0.54371234417458658</v>
+      </c>
+      <c r="H34" s="9">
+        <f>(D33 * Prices!F32) / $F33</f>
+        <v>0.24222890105406109</v>
+      </c>
+      <c r="I34" s="9">
+        <f>(E33 * Prices!G32) / $F33</f>
+        <v>0.21405875477135242</v>
       </c>
     </row>
   </sheetData>
@@ -2054,8 +2901,8 @@
         <v>45659</v>
       </c>
       <c r="B3" s="7">
-        <f>B2 * Expected_Weights!E4</f>
-        <v>0.95500000000000007</v>
+        <f>B2 * Expected_Weights!F4</f>
+        <v>0.97875000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -2063,8 +2910,8 @@
         <v>45660</v>
       </c>
       <c r="B4" s="7">
-        <f>B3 * Expected_Weights!E5</f>
-        <v>1.01</v>
+        <f>B3 * Expected_Weights!F5</f>
+        <v>1.0075000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -2072,8 +2919,8 @@
         <v>45661</v>
       </c>
       <c r="B5" s="7">
-        <f>B4 * Expected_Weights!E6</f>
-        <v>0.96500000000000008</v>
+        <f>B4 * Expected_Weights!F6</f>
+        <v>0.98624999999999985</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -2081,8 +2928,8 @@
         <v>45662</v>
       </c>
       <c r="B6" s="7">
-        <f>B5 * Expected_Weights!E7</f>
-        <v>1.0200000000000002</v>
+        <f>B5 * Expected_Weights!F7</f>
+        <v>1.0149999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
@@ -2090,8 +2937,8 @@
         <v>45663</v>
       </c>
       <c r="B7" s="7">
-        <f>B6 * Expected_Weights!E8</f>
-        <v>0.9750000000000002</v>
+        <f>B6 * Expected_Weights!F8</f>
+        <v>0.99374999999999991</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
@@ -2099,8 +2946,8 @@
         <v>45664</v>
       </c>
       <c r="B8" s="7">
-        <f>B7 * Expected_Weights!E9</f>
-        <v>1.0300000000000002</v>
+        <f>B7 * Expected_Weights!F9</f>
+        <v>1.0225</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
@@ -2108,8 +2955,8 @@
         <v>45665</v>
       </c>
       <c r="B9" s="7">
-        <f>B8 * Expected_Weights!E10</f>
-        <v>0.98500000000000054</v>
+        <f>B8 * Expected_Weights!F10</f>
+        <v>1.00125</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
@@ -2117,8 +2964,8 @@
         <v>45666</v>
       </c>
       <c r="B10" s="7">
-        <f>B9 * Expected_Weights!E11</f>
-        <v>1.0400000000000005</v>
+        <f>B9 * Expected_Weights!F11</f>
+        <v>1.0299999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
@@ -2126,8 +2973,8 @@
         <v>45667</v>
       </c>
       <c r="B11" s="7">
-        <f>B10 * Expected_Weights!E12</f>
-        <v>0.99500000000000044</v>
+        <f>B10 * Expected_Weights!F12</f>
+        <v>1.0087499999999998</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
@@ -2135,8 +2982,8 @@
         <v>45668</v>
       </c>
       <c r="B12" s="7">
-        <f>B11 * Expected_Weights!E13</f>
-        <v>1.0500000000000005</v>
+        <f>B11 * Expected_Weights!F13</f>
+        <v>1.0374999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
@@ -2144,8 +2991,8 @@
         <v>45669</v>
       </c>
       <c r="B13" s="7">
-        <f>B12 * Expected_Weights!E14</f>
-        <v>1.0050000000000003</v>
+        <f>B12 * Expected_Weights!F14</f>
+        <v>1.0162499999999999</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
@@ -2153,8 +3000,8 @@
         <v>45670</v>
       </c>
       <c r="B14" s="7">
-        <f>B13 * Expected_Weights!E15</f>
-        <v>1.0627950450450454</v>
+        <f>B13 * Expected_Weights!F15</f>
+        <v>1.0466703265765762</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
@@ -2162,8 +3009,8 @@
         <v>45671</v>
       </c>
       <c r="B15" s="7">
-        <f>B14 * Expected_Weights!E16</f>
-        <v>1.0145067567567572</v>
+        <f>B14 * Expected_Weights!F16</f>
+        <v>1.0234552364864862</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
@@ -2171,8 +3018,8 @@
         <v>45672</v>
       </c>
       <c r="B16" s="7">
-        <f>B15 * Expected_Weights!E17</f>
-        <v>1.0723018018018022</v>
+        <f>B15 * Expected_Weights!F17</f>
+        <v>1.0538755630630627</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
@@ -2180,8 +3027,8 @@
         <v>45673</v>
       </c>
       <c r="B17" s="7">
-        <f>B16 * Expected_Weights!E18</f>
-        <v>1.024013513513514</v>
+        <f>B16 * Expected_Weights!F18</f>
+        <v>1.0306604729729727</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
@@ -2189,8 +3036,8 @@
         <v>45674</v>
       </c>
       <c r="B18" s="7">
-        <f>B17 * Expected_Weights!E19</f>
-        <v>1.0818085585585593</v>
+        <f>B17 * Expected_Weights!F19</f>
+        <v>1.0610807995495495</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
@@ -2198,8 +3045,8 @@
         <v>45675</v>
       </c>
       <c r="B19" s="7">
-        <f>B18 * Expected_Weights!E20</f>
-        <v>1.033520270270271</v>
+        <f>B18 * Expected_Weights!F20</f>
+        <v>1.0378657094594594</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
@@ -2207,8 +3054,8 @@
         <v>45676</v>
       </c>
       <c r="B20" s="7">
-        <f>B19 * Expected_Weights!E21</f>
-        <v>1.0913153153153161</v>
+        <f>B19 * Expected_Weights!F21</f>
+        <v>1.068286036036036</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
@@ -2216,8 +3063,8 @@
         <v>45677</v>
       </c>
       <c r="B21" s="7">
-        <f>B20 * Expected_Weights!E22</f>
-        <v>1.0430270270270279</v>
+        <f>B20 * Expected_Weights!F22</f>
+        <v>1.0447047054883389</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
@@ -2225,8 +3072,8 @@
         <v>45678</v>
       </c>
       <c r="B22" s="7">
-        <f>B21 * Expected_Weights!E23</f>
-        <v>1.1008220720720732</v>
+        <f>B21 * Expected_Weights!F23</f>
+        <v>1.0747587916073085</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
@@ -2234,8 +3081,8 @@
         <v>45679</v>
       </c>
       <c r="B23" s="7">
-        <f>B22 * Expected_Weights!E24</f>
-        <v>1.0525337837837847</v>
+        <f>B22 * Expected_Weights!F24</f>
+        <v>1.0511774610596114</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
@@ -2243,8 +3090,8 @@
         <v>45680</v>
       </c>
       <c r="B24" s="7">
-        <f>B23 * Expected_Weights!E25</f>
-        <v>1.11032882882883</v>
+        <f>B23 * Expected_Weights!F25</f>
+        <v>1.0812315471785812</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
@@ -2252,8 +3099,8 @@
         <v>45681</v>
       </c>
       <c r="B25" s="7">
-        <f>B24 * Expected_Weights!E26</f>
-        <v>1.0620405405405415</v>
+        <f>B24 * Expected_Weights!F26</f>
+        <v>1.0576502166308839</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
@@ -2261,8 +3108,8 @@
         <v>45682</v>
       </c>
       <c r="B26" s="7">
-        <f>B25 * Expected_Weights!E27</f>
-        <v>1.1198355855855866</v>
+        <f>B25 * Expected_Weights!F27</f>
+        <v>1.0877043027498534</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
@@ -2270,8 +3117,8 @@
         <v>45683</v>
       </c>
       <c r="B27" s="7">
-        <f>B26 * Expected_Weights!E28</f>
-        <v>1.0715472972972984</v>
+        <f>B26 * Expected_Weights!F28</f>
+        <v>1.0641229722021566</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
@@ -2279,8 +3126,8 @@
         <v>45684</v>
       </c>
       <c r="B28" s="7">
-        <f>B27 * Expected_Weights!E29</f>
-        <v>1.1326016810810822</v>
+        <f>B27 * Expected_Weights!F29</f>
+        <v>1.0941770583211263</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
@@ -2288,8 +3135,8 @@
         <v>45685</v>
       </c>
       <c r="B29" s="7">
-        <f>B28 * Expected_Weights!E30</f>
-        <v>1.0805482945945957</v>
+        <f>B28 * Expected_Weights!F30</f>
+        <v>1.0705957277734293</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
@@ -2297,8 +3144,8 @@
         <v>45686</v>
       </c>
       <c r="B30" s="7">
-        <f>B29 * Expected_Weights!E31</f>
-        <v>1.1416026783783795</v>
+        <f>B29 * Expected_Weights!F31</f>
+        <v>1.100649813892399</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
@@ -2306,8 +3153,8 @@
         <v>45687</v>
       </c>
       <c r="B31" s="7">
-        <f>B30 * Expected_Weights!E32</f>
-        <v>1.089549291891893</v>
+        <f>B30 * Expected_Weights!F32</f>
+        <v>1.077068483344702</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
@@ -2315,8 +3162,8 @@
         <v>45688</v>
       </c>
       <c r="B32" s="7">
-        <f>B31 * Expected_Weights!E33</f>
-        <v>1.1506036756756768</v>
+        <f>B31 * Expected_Weights!F33</f>
+        <v>1.1071225694636715</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.4">
@@ -2324,8 +3171,8 @@
         <v>45689</v>
       </c>
       <c r="B33" s="7">
-        <f>B32 * Expected_Weights!E34</f>
-        <v>1.0985502891891901</v>
+        <f>B32 * Expected_Weights!F34</f>
+        <v>1.0835412389159746</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_rb_sigma.xlsx
+++ b/public/tests/data/test_rb_sigma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB43F57-A5AF-48F0-BCC0-15E46E9C7003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F699CF-9FDC-4DE4-9D96-8FE8FC12A1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3256,25 +3256,25 @@
         <v>40</v>
       </c>
       <c r="F2" s="5">
-        <v>9.86</v>
+        <v>8.35</v>
       </c>
       <c r="G2" s="5">
-        <v>202.66</v>
+        <v>157.37</v>
       </c>
       <c r="H2" s="5">
-        <v>79.42</v>
+        <v>39.79</v>
       </c>
       <c r="I2" s="5">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="J2">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="K2" s="5">
-        <v>-4.5999999999999996</v>
+        <v>-2.2200000000000002</v>
       </c>
       <c r="L2" s="5">
-        <v>-4.4400000000000004</v>
+        <v>-2.14</v>
       </c>
       <c r="M2" t="s">
         <v>29</v>
